--- a/inasistencias-6A-electronicaYsistDeComTP/Alumnos-6A-EletronicaYsistDeComTP.xlsx
+++ b/inasistencias-6A-electronicaYsistDeComTP/Alumnos-6A-EletronicaYsistDeComTP.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="304">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -44,6 +44,9 @@
     <t xml:space="preserve">Dirección de correo</t>
   </si>
   <si>
+    <t xml:space="preserve">obs</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lucila Yanel</t>
   </si>
   <si>
@@ -56,6 +59,12 @@
     <t xml:space="preserve">P</t>
   </si>
   <si>
+    <t xml:space="preserve">Intensifica Matematica 16:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lourdes Elizabeth</t>
   </si>
   <si>
@@ -92,6 +101,9 @@
     <t xml:space="preserve">sathyxzz@gmail.com</t>
   </si>
   <si>
+    <t xml:space="preserve">T</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
@@ -137,6 +149,15 @@
     <t xml:space="preserve">dimeofrancisco@gmail.com</t>
   </si>
   <si>
+    <t xml:space="preserve">Recursa 15:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recursan 15:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recursando</t>
+  </si>
+  <si>
     <t xml:space="preserve">Facundo Agustin</t>
   </si>
   <si>
@@ -164,6 +185,9 @@
     <t xml:space="preserve">victoriacruz.alzu@gmail.com</t>
   </si>
   <si>
+    <t xml:space="preserve">Recursando</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tobias</t>
   </si>
   <si>
@@ -248,12 +272,63 @@
     <t xml:space="preserve">olimpiadas</t>
   </si>
   <si>
-    <t xml:space="preserve">toal</t>
+    <t xml:space="preserve">total</t>
   </si>
   <si>
     <t xml:space="preserve">Grupos </t>
   </si>
   <si>
+    <t xml:space="preserve">Pregunta 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preg 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parte2- preg 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parte 2- preg 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parte 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0-Tp alarmas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proy 1- Cto Resonante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preg 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preg 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">frecuencia de resonancia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">procedimiento Fcia de rsonancia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">distraida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no sba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no sabe</t>
+  </si>
+  <si>
     <t xml:space="preserve">positivos</t>
   </si>
   <si>
@@ -804,9 +879,6 @@
   </si>
   <si>
     <t xml:space="preserve">5 minutos 11 segundos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total</t>
   </si>
   <si>
     <t xml:space="preserve">45 minutos 55 segundos</t>
@@ -876,9 +948,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="166" formatCode="hh:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -946,7 +1019,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -967,6 +1040,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -976,23 +1057,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1107,15 +1171,22 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:FF1048576"/>
+  <dimension ref="A1:FJ28"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.34"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16197" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="8.68"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="6" min="6" style="1" width="8.75"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="7" style="1" width="12.84"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="9" min="8" style="1" width="8.75"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="1" width="25.03"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="11" min="11" style="1" width="8.75"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="12" style="1" width="10.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="10.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16201" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1143,127 +1214,139 @@
       <c r="F2" s="3" t="n">
         <v>46098</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3" t="n">
         <v>46105</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="I2" s="3" t="n">
         <v>46112</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="J2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="3" t="n">
         <v>46119</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="L2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="3" t="n">
         <v>46126</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="N2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O2" s="3" t="n">
         <v>46133</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="P2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="3" t="n">
         <v>46140</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="R2" s="3" t="n">
         <v>46147</v>
       </c>
-      <c r="N2" s="3" t="n">
-        <v>46154</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>46161</v>
-      </c>
-      <c r="P2" s="3" t="n">
+      <c r="S2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T2" s="3" t="n">
         <v>46168</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="U2" s="3" t="n">
         <v>46175</v>
       </c>
-      <c r="R2" s="3" t="n">
+      <c r="V2" s="3" t="n">
         <v>46182</v>
       </c>
-      <c r="S2" s="3" t="n">
+      <c r="W2" s="3" t="n">
         <v>46189</v>
       </c>
-      <c r="T2" s="3" t="n">
+      <c r="X2" s="3" t="n">
         <v>46196</v>
       </c>
-      <c r="U2" s="3" t="n">
+      <c r="Y2" s="3" t="n">
         <v>46203</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="Z2" s="3" t="n">
         <v>46210</v>
       </c>
-      <c r="W2" s="3" t="n">
+      <c r="AA2" s="3" t="n">
         <v>46217</v>
       </c>
-      <c r="X2" s="3" t="n">
+      <c r="AB2" s="3" t="n">
         <v>46224</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="AC2" s="3" t="n">
         <v>46231</v>
       </c>
-      <c r="Z2" s="3" t="n">
+      <c r="AD2" s="3" t="n">
         <v>46238</v>
       </c>
-      <c r="AA2" s="3" t="n">
+      <c r="AE2" s="3" t="n">
         <v>46245</v>
       </c>
-      <c r="AB2" s="3" t="n">
+      <c r="AF2" s="3" t="n">
         <v>46252</v>
       </c>
-      <c r="AC2" s="3" t="n">
+      <c r="AG2" s="3" t="n">
         <v>46259</v>
       </c>
-      <c r="AD2" s="3" t="n">
+      <c r="AH2" s="3" t="n">
         <v>46266</v>
       </c>
-      <c r="AE2" s="3" t="n">
+      <c r="AI2" s="3" t="n">
         <v>46273</v>
       </c>
-      <c r="AF2" s="3" t="n">
+      <c r="AJ2" s="3" t="n">
         <v>46280</v>
       </c>
-      <c r="AG2" s="3" t="n">
+      <c r="AK2" s="3" t="n">
         <v>46287</v>
       </c>
-      <c r="AH2" s="3" t="n">
+      <c r="AL2" s="3" t="n">
         <v>46294</v>
       </c>
-      <c r="AI2" s="3" t="n">
+      <c r="AM2" s="3" t="n">
         <v>46301</v>
       </c>
-      <c r="AJ2" s="3" t="n">
+      <c r="AN2" s="3" t="n">
         <v>46308</v>
       </c>
-      <c r="AK2" s="3" t="n">
+      <c r="AO2" s="3" t="n">
         <v>46315</v>
       </c>
-      <c r="AL2" s="3" t="n">
+      <c r="AP2" s="3" t="n">
         <v>46322</v>
       </c>
-      <c r="AM2" s="3" t="n">
+      <c r="AQ2" s="3" t="n">
         <v>46329</v>
       </c>
-      <c r="AN2" s="3" t="n">
+      <c r="AR2" s="3" t="n">
         <v>46336</v>
       </c>
-      <c r="AO2" s="3" t="n">
+      <c r="AS2" s="3" t="n">
         <v>46343</v>
       </c>
-      <c r="AP2" s="3" t="n">
+      <c r="AT2" s="3" t="n">
         <v>46350</v>
       </c>
-      <c r="AQ2" s="3" t="n">
+      <c r="AU2" s="3" t="n">
         <v>46357</v>
       </c>
-      <c r="AR2" s="3" t="n">
+      <c r="AV2" s="3" t="n">
         <v>46364</v>
       </c>
-      <c r="AS2" s="3" t="n">
+      <c r="AW2" s="3" t="n">
         <v>46371</v>
       </c>
-      <c r="AT2" s="3" t="n">
+      <c r="AX2" s="3" t="n">
         <v>46378</v>
       </c>
-      <c r="AU2" s="3" t="n">
+      <c r="AY2" s="3" t="n">
         <v>46385</v>
       </c>
     </row>
@@ -1272,16 +1355,40 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1289,16 +1396,40 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>7</v>
+      <c r="K4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1306,16 +1437,37 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1323,16 +1475,37 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1340,16 +1513,40 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>0.680555555555556</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1357,31 +1554,45 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
+      <c r="O8" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
+      <c r="Q8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="0"/>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
@@ -1525,22 +1736,47 @@
       <c r="FD8" s="1"/>
       <c r="FE8" s="1"/>
       <c r="FF8" s="1"/>
+      <c r="FG8" s="1"/>
+      <c r="FH8" s="1"/>
+      <c r="FI8" s="1"/>
+      <c r="FJ8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1548,16 +1784,37 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1565,16 +1822,37 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1582,31 +1860,53 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
+      <c r="I12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
+      <c r="Q12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" s="0"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
@@ -1750,71 +2050,141 @@
       <c r="FD12" s="1"/>
       <c r="FE12" s="1"/>
       <c r="FF12" s="1"/>
+      <c r="FG12" s="1"/>
+      <c r="FH12" s="1"/>
+      <c r="FI12" s="1"/>
+      <c r="FJ12" s="1"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="0"/>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="0"/>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
+      <c r="Q15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" s="0"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
@@ -1958,71 +2328,139 @@
       <c r="FD15" s="1"/>
       <c r="FE15" s="1"/>
       <c r="FF15" s="1"/>
+      <c r="FG15" s="1"/>
+      <c r="FH15" s="1"/>
+      <c r="FI15" s="1"/>
+      <c r="FJ15" s="1"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="0"/>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="0"/>
     </row>
     <row r="18" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
+      <c r="I18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
+      <c r="M18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
+      <c r="Q18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="S18" s="0"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
@@ -2166,37 +2604,57 @@
       <c r="FD18" s="1"/>
       <c r="FE18" s="1"/>
       <c r="FF18" s="1"/>
+      <c r="FG18" s="1"/>
+      <c r="FH18" s="1"/>
+      <c r="FI18" s="1"/>
+      <c r="FJ18" s="1"/>
     </row>
     <row r="19" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+      <c r="I19" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
+      <c r="M19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
+      <c r="Q19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="S19" s="0"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
@@ -2340,88 +2798,187 @@
       <c r="FD19" s="1"/>
       <c r="FE19" s="1"/>
       <c r="FF19" s="1"/>
+      <c r="FG19" s="1"/>
+      <c r="FH19" s="1"/>
+      <c r="FI19" s="1"/>
+      <c r="FJ19" s="1"/>
     </row>
     <row r="20" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="S20" s="0"/>
     </row>
     <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="0"/>
     </row>
     <row r="22" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="0"/>
     </row>
     <row r="23" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+      <c r="I23" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
+      <c r="K23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
+      <c r="Q23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="R23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="S23" s="0"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
@@ -2565,40 +3122,209 @@
       <c r="FD23" s="1"/>
       <c r="FE23" s="1"/>
       <c r="FF23" s="1"/>
+      <c r="FG23" s="1"/>
+      <c r="FH23" s="1"/>
+      <c r="FI23" s="1"/>
+      <c r="FJ23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E24" s="1" t="n">
         <f aca="false">COUNTIF(E3:E23,"P")</f>
         <v>21</v>
       </c>
+      <c r="F24" s="1" t="n">
+        <f aca="false">COUNTIF(F3:F23,"P")</f>
+        <v>15</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <f aca="false">COUNTIF(I3:I23,"P")</f>
+        <v>17</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <f aca="false">COUNTIF(K3:K23,"P")</f>
+        <v>12</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <f aca="false">COUNTIF(M3:M23,"P")</f>
+        <v>14</v>
+      </c>
+      <c r="O24" s="1" t="n">
+        <f aca="false">COUNTIF(O3:O23,"P")</f>
+        <v>14</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1" t="n">
+        <f aca="false">COUNTIF(Q3:Q23,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="R24" s="1" t="n">
+        <f aca="false">COUNTIF(R3:R23,"P")</f>
+        <v>14</v>
+      </c>
+      <c r="S24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <f aca="false">COUNTIF(E3:E23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <f aca="false">COUNTIF(F3:F23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <f aca="false">COUNTIF(I3:I23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <f aca="false">COUNTIF(K3:K23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <f aca="false">COUNTIF(M3:M23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="1" t="n">
+        <f aca="false">COUNTIF(O3:O23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1" t="n">
+        <f aca="false">COUNTIF(Q3:Q23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <f aca="false">COUNTIF(R3:R23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>70</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <f aca="false">COUNTIF(E3:E23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <f aca="false">COUNTIF(F3:F23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <f aca="false">COUNTIF(I3:I23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <f aca="false">COUNTIF(K3:K23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <f aca="false">COUNTIF(M3:M23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="1" t="n">
+        <f aca="false">COUNTIF(O3:O23,"T")</f>
+        <v>1</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1" t="n">
+        <f aca="false">COUNTIF(Q3:Q23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <f aca="false">COUNTIF(R3:R23,"T")</f>
+        <v>1</v>
+      </c>
+      <c r="S26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
-        <v>71</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <f aca="false">COUNTIF(E3:E23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <f aca="false">COUNTIF(F3:F23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <f aca="false">COUNTIF(I3:I23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <f aca="false">COUNTIF(K3:K23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <f aca="false">COUNTIF(M3:M23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="1" t="n">
+        <f aca="false">COUNTIF(O3:O23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1" t="n">
+        <f aca="false">COUNTIF(Q3:Q23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <f aca="false">COUNTIF(R3:R23,"O")</f>
+        <v>0</v>
+      </c>
+      <c r="S27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>80</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <f aca="false">SUM(E24:E27)</f>
+        <v>21</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <f aca="false">SUM(F24:F27)</f>
+        <v>15</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <f aca="false">SUM(I24:I27)</f>
+        <v>17</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <f aca="false">SUM(K24:K27)</f>
+        <v>12</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <f aca="false">SUM(M24:M27)</f>
+        <v>14</v>
+      </c>
+      <c r="O28" s="1" t="n">
+        <f aca="false">SUM(O24:O27)</f>
+        <v>15</v>
+      </c>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1" t="n">
+        <f aca="false">SUM(Q24:Q27)</f>
+        <v>13</v>
+      </c>
+      <c r="R28" s="1" t="n">
+        <f aca="false">SUM(R24:R27)</f>
+        <v>15</v>
+      </c>
+      <c r="S28" s="1"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2632,19 +3358,19 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2652,7 +3378,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -2666,16 +3392,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -2689,7 +3415,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -2703,16 +3429,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>8</v>
@@ -2726,7 +3452,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -2740,7 +3466,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -2754,16 +3480,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>6</v>
@@ -2777,16 +3503,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -2805,13 +3531,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>9</v>
@@ -2822,16 +3548,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -2850,13 +3576,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>6</v>
@@ -2867,7 +3593,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>1</v>
@@ -2881,16 +3607,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>10</v>
@@ -2904,16 +3630,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9</v>
@@ -2927,7 +3653,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -2941,16 +3667,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>6</v>
@@ -2964,7 +3690,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -2978,7 +3704,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>1</v>
@@ -2992,7 +3718,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>1</v>
@@ -3006,7 +3732,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>1</v>
@@ -3020,7 +3746,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>1</v>
@@ -3034,7 +3760,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>1</v>
@@ -3048,16 +3774,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>7</v>
@@ -3076,13 +3802,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>5</v>
@@ -3090,13 +3816,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>5</v>
@@ -3107,7 +3833,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>1</v>
@@ -3118,7 +3844,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G28" s="1" t="s">
-        <v>258</v>
+        <v>80</v>
       </c>
       <c r="I28" s="1" t="n">
         <f aca="false">COUNTIF(I2:I27,"&gt;0")</f>
@@ -3162,10 +3888,10 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3173,16 +3899,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>8.5</v>
@@ -3193,16 +3919,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>7</v>
@@ -3213,16 +3939,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -3233,16 +3959,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>9</v>
@@ -3253,7 +3979,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -3264,16 +3990,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>10</v>
@@ -3284,16 +4010,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>8.75</v>
@@ -3304,16 +4030,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -3324,16 +4050,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8.75</v>
@@ -3344,16 +4070,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>8.25</v>
@@ -3364,16 +4090,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>8.75</v>
@@ -3384,16 +4110,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9.5</v>
@@ -3404,16 +4130,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>7.25</v>
@@ -3424,16 +4150,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>9.25</v>
@@ -3444,16 +4170,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>7.25</v>
@@ -3464,7 +4190,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -3475,16 +4201,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>9</v>
@@ -3495,16 +4221,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>8.5</v>
@@ -3515,16 +4241,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>8.5</v>
@@ -3535,16 +4261,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -3555,16 +4281,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9.25</v>
@@ -3575,16 +4301,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -3606,13 +4332,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AMM1048576"/>
+  <dimension ref="A1:AMN23"/>
   <sheetFormatPr defaultColWidth="9.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="983" min="983" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16341" style="0" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="5" min="4" style="0" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="1" width="12.98"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="8" min="7" style="0" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="19.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="21.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="984" min="984" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16342" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3625,1069 +4356,632 @@
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AKV3" s="0"/>
-      <c r="AKW3" s="0"/>
-      <c r="AKX3" s="0"/>
-      <c r="AKY3" s="0"/>
-      <c r="AKZ3" s="0"/>
-      <c r="ALA3" s="0"/>
-      <c r="ALB3" s="0"/>
-      <c r="ALC3" s="0"/>
-      <c r="ALD3" s="0"/>
-      <c r="ALE3" s="0"/>
-      <c r="ALF3" s="0"/>
-      <c r="ALG3" s="0"/>
-      <c r="ALH3" s="0"/>
-      <c r="ALI3" s="0"/>
-      <c r="ALJ3" s="0"/>
-      <c r="ALK3" s="0"/>
-      <c r="ALL3" s="0"/>
-      <c r="ALM3" s="0"/>
-      <c r="ALN3" s="0"/>
-      <c r="ALO3" s="0"/>
-      <c r="ALP3" s="0"/>
-      <c r="ALQ3" s="0"/>
-      <c r="ALR3" s="0"/>
-      <c r="ALS3" s="0"/>
-      <c r="ALT3" s="0"/>
-      <c r="ALU3" s="0"/>
-      <c r="ALV3" s="0"/>
-      <c r="ALW3" s="0"/>
-      <c r="ALX3" s="0"/>
-      <c r="ALY3" s="0"/>
-      <c r="ALZ3" s="0"/>
-      <c r="AMA3" s="0"/>
-      <c r="AMB3" s="0"/>
-      <c r="AMC3" s="0"/>
-      <c r="AMD3" s="0"/>
-      <c r="AME3" s="0"/>
-      <c r="AMF3" s="0"/>
-      <c r="AMG3" s="0"/>
-      <c r="AMH3" s="0"/>
-      <c r="AMI3" s="0"/>
-      <c r="AMJ3" s="0"/>
-      <c r="AMK3" s="0"/>
-      <c r="AML3" s="0"/>
-      <c r="AMM3" s="0"/>
-    </row>
-    <row r="4" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I3" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AKV4" s="0"/>
-      <c r="AKW4" s="0"/>
-      <c r="AKX4" s="0"/>
-      <c r="AKY4" s="0"/>
-      <c r="AKZ4" s="0"/>
-      <c r="ALA4" s="0"/>
-      <c r="ALB4" s="0"/>
-      <c r="ALC4" s="0"/>
-      <c r="ALD4" s="0"/>
-      <c r="ALE4" s="0"/>
-      <c r="ALF4" s="0"/>
-      <c r="ALG4" s="0"/>
-      <c r="ALH4" s="0"/>
-      <c r="ALI4" s="0"/>
-      <c r="ALJ4" s="0"/>
-      <c r="ALK4" s="0"/>
-      <c r="ALL4" s="0"/>
-      <c r="ALM4" s="0"/>
-      <c r="ALN4" s="0"/>
-      <c r="ALO4" s="0"/>
-      <c r="ALP4" s="0"/>
-      <c r="ALQ4" s="0"/>
-      <c r="ALR4" s="0"/>
-      <c r="ALS4" s="0"/>
-      <c r="ALT4" s="0"/>
-      <c r="ALU4" s="0"/>
-      <c r="ALV4" s="0"/>
-      <c r="ALW4" s="0"/>
-      <c r="ALX4" s="0"/>
-      <c r="ALY4" s="0"/>
-      <c r="ALZ4" s="0"/>
-      <c r="AMA4" s="0"/>
-      <c r="AMB4" s="0"/>
-      <c r="AMC4" s="0"/>
-      <c r="AMD4" s="0"/>
-      <c r="AME4" s="0"/>
-      <c r="AMF4" s="0"/>
-      <c r="AMG4" s="0"/>
-      <c r="AMH4" s="0"/>
-      <c r="AMI4" s="0"/>
-      <c r="AMJ4" s="0"/>
-      <c r="AMK4" s="0"/>
-      <c r="AML4" s="0"/>
-      <c r="AMM4" s="0"/>
-    </row>
-    <row r="5" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AKV5" s="0"/>
-      <c r="AKW5" s="0"/>
-      <c r="AKX5" s="0"/>
-      <c r="AKY5" s="0"/>
-      <c r="AKZ5" s="0"/>
-      <c r="ALA5" s="0"/>
-      <c r="ALB5" s="0"/>
-      <c r="ALC5" s="0"/>
-      <c r="ALD5" s="0"/>
-      <c r="ALE5" s="0"/>
-      <c r="ALF5" s="0"/>
-      <c r="ALG5" s="0"/>
-      <c r="ALH5" s="0"/>
-      <c r="ALI5" s="0"/>
-      <c r="ALJ5" s="0"/>
-      <c r="ALK5" s="0"/>
-      <c r="ALL5" s="0"/>
-      <c r="ALM5" s="0"/>
-      <c r="ALN5" s="0"/>
-      <c r="ALO5" s="0"/>
-      <c r="ALP5" s="0"/>
-      <c r="ALQ5" s="0"/>
-      <c r="ALR5" s="0"/>
-      <c r="ALS5" s="0"/>
-      <c r="ALT5" s="0"/>
-      <c r="ALU5" s="0"/>
-      <c r="ALV5" s="0"/>
-      <c r="ALW5" s="0"/>
-      <c r="ALX5" s="0"/>
-      <c r="ALY5" s="0"/>
-      <c r="ALZ5" s="0"/>
-      <c r="AMA5" s="0"/>
-      <c r="AMB5" s="0"/>
-      <c r="AMC5" s="0"/>
-      <c r="AMD5" s="0"/>
-      <c r="AME5" s="0"/>
-      <c r="AMF5" s="0"/>
-      <c r="AMG5" s="0"/>
-      <c r="AMH5" s="0"/>
-      <c r="AMI5" s="0"/>
-      <c r="AMJ5" s="0"/>
-      <c r="AMK5" s="0"/>
-      <c r="AML5" s="0"/>
-      <c r="AMM5" s="0"/>
-    </row>
-    <row r="6" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I5" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AKV6" s="0"/>
-      <c r="AKW6" s="0"/>
-      <c r="AKX6" s="0"/>
-      <c r="AKY6" s="0"/>
-      <c r="AKZ6" s="0"/>
-      <c r="ALA6" s="0"/>
-      <c r="ALB6" s="0"/>
-      <c r="ALC6" s="0"/>
-      <c r="ALD6" s="0"/>
-      <c r="ALE6" s="0"/>
-      <c r="ALF6" s="0"/>
-      <c r="ALG6" s="0"/>
-      <c r="ALH6" s="0"/>
-      <c r="ALI6" s="0"/>
-      <c r="ALJ6" s="0"/>
-      <c r="ALK6" s="0"/>
-      <c r="ALL6" s="0"/>
-      <c r="ALM6" s="0"/>
-      <c r="ALN6" s="0"/>
-      <c r="ALO6" s="0"/>
-      <c r="ALP6" s="0"/>
-      <c r="ALQ6" s="0"/>
-      <c r="ALR6" s="0"/>
-      <c r="ALS6" s="0"/>
-      <c r="ALT6" s="0"/>
-      <c r="ALU6" s="0"/>
-      <c r="ALV6" s="0"/>
-      <c r="ALW6" s="0"/>
-      <c r="ALX6" s="0"/>
-      <c r="ALY6" s="0"/>
-      <c r="ALZ6" s="0"/>
-      <c r="AMA6" s="0"/>
-      <c r="AMB6" s="0"/>
-      <c r="AMC6" s="0"/>
-      <c r="AMD6" s="0"/>
-      <c r="AME6" s="0"/>
-      <c r="AMF6" s="0"/>
-      <c r="AMG6" s="0"/>
-      <c r="AMH6" s="0"/>
-      <c r="AMI6" s="0"/>
-      <c r="AMJ6" s="0"/>
-      <c r="AMK6" s="0"/>
-      <c r="AML6" s="0"/>
-      <c r="AMM6" s="0"/>
-    </row>
-    <row r="7" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I6" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AKV7" s="0"/>
-      <c r="AKW7" s="0"/>
-      <c r="AKX7" s="0"/>
-      <c r="AKY7" s="0"/>
-      <c r="AKZ7" s="0"/>
-      <c r="ALA7" s="0"/>
-      <c r="ALB7" s="0"/>
-      <c r="ALC7" s="0"/>
-      <c r="ALD7" s="0"/>
-      <c r="ALE7" s="0"/>
-      <c r="ALF7" s="0"/>
-      <c r="ALG7" s="0"/>
-      <c r="ALH7" s="0"/>
-      <c r="ALI7" s="0"/>
-      <c r="ALJ7" s="0"/>
-      <c r="ALK7" s="0"/>
-      <c r="ALL7" s="0"/>
-      <c r="ALM7" s="0"/>
-      <c r="ALN7" s="0"/>
-      <c r="ALO7" s="0"/>
-      <c r="ALP7" s="0"/>
-      <c r="ALQ7" s="0"/>
-      <c r="ALR7" s="0"/>
-      <c r="ALS7" s="0"/>
-      <c r="ALT7" s="0"/>
-      <c r="ALU7" s="0"/>
-      <c r="ALV7" s="0"/>
-      <c r="ALW7" s="0"/>
-      <c r="ALX7" s="0"/>
-      <c r="ALY7" s="0"/>
-      <c r="ALZ7" s="0"/>
-      <c r="AMA7" s="0"/>
-      <c r="AMB7" s="0"/>
-      <c r="AMC7" s="0"/>
-      <c r="AMD7" s="0"/>
-      <c r="AME7" s="0"/>
-      <c r="AMF7" s="0"/>
-      <c r="AMG7" s="0"/>
-      <c r="AMH7" s="0"/>
-      <c r="AMI7" s="0"/>
-      <c r="AMJ7" s="0"/>
-      <c r="AMK7" s="0"/>
-      <c r="AML7" s="0"/>
-      <c r="AMM7" s="0"/>
-    </row>
-    <row r="8" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I7" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AKU8" s="1"/>
-      <c r="AKV8" s="0"/>
-      <c r="AKW8" s="0"/>
-      <c r="AKX8" s="0"/>
-      <c r="AKY8" s="0"/>
-      <c r="AKZ8" s="0"/>
-      <c r="ALA8" s="0"/>
-      <c r="ALB8" s="0"/>
-      <c r="ALC8" s="0"/>
-      <c r="ALD8" s="0"/>
-      <c r="ALE8" s="0"/>
-      <c r="ALF8" s="0"/>
-      <c r="ALG8" s="0"/>
-      <c r="ALH8" s="0"/>
-      <c r="ALI8" s="0"/>
-      <c r="ALJ8" s="0"/>
-      <c r="ALK8" s="0"/>
-      <c r="ALL8" s="0"/>
-      <c r="ALM8" s="0"/>
-      <c r="ALN8" s="0"/>
-      <c r="ALO8" s="0"/>
-      <c r="ALP8" s="0"/>
-      <c r="ALQ8" s="0"/>
-      <c r="ALR8" s="0"/>
-      <c r="ALS8" s="0"/>
-      <c r="ALT8" s="0"/>
-      <c r="ALU8" s="0"/>
-      <c r="ALV8" s="0"/>
-      <c r="ALW8" s="0"/>
-      <c r="ALX8" s="0"/>
-      <c r="ALY8" s="0"/>
-      <c r="ALZ8" s="0"/>
-      <c r="AMA8" s="0"/>
-      <c r="AMB8" s="0"/>
-      <c r="AMC8" s="0"/>
-      <c r="AMD8" s="0"/>
-      <c r="AME8" s="0"/>
-      <c r="AMF8" s="0"/>
-      <c r="AMG8" s="0"/>
-      <c r="AMH8" s="0"/>
-      <c r="AMI8" s="0"/>
-      <c r="AMJ8" s="0"/>
-      <c r="AMK8" s="0"/>
-      <c r="AML8" s="0"/>
-      <c r="AMM8" s="0"/>
-    </row>
-    <row r="9" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AKV8" s="1"/>
+      <c r="AKW8" s="1"/>
+      <c r="AKX8" s="1"/>
+      <c r="AKY8" s="1"/>
+      <c r="AKZ8" s="1"/>
+      <c r="ALA8" s="1"/>
+      <c r="ALB8" s="1"/>
+      <c r="ALC8" s="1"/>
+      <c r="ALD8" s="1"/>
+      <c r="ALE8" s="1"/>
+      <c r="ALF8" s="1"/>
+      <c r="ALG8" s="1"/>
+      <c r="ALH8" s="1"/>
+      <c r="ALI8" s="1"/>
+      <c r="ALJ8" s="1"/>
+      <c r="ALK8" s="1"/>
+      <c r="ALL8" s="1"/>
+      <c r="ALM8" s="1"/>
+      <c r="ALN8" s="1"/>
+      <c r="ALO8" s="1"/>
+      <c r="ALP8" s="1"/>
+      <c r="ALQ8" s="1"/>
+      <c r="ALR8" s="1"/>
+      <c r="ALS8" s="1"/>
+      <c r="ALT8" s="1"/>
+      <c r="ALU8" s="1"/>
+      <c r="ALV8" s="1"/>
+      <c r="ALW8" s="1"/>
+      <c r="ALX8" s="1"/>
+      <c r="ALY8" s="1"/>
+      <c r="ALZ8" s="1"/>
+      <c r="AMA8" s="1"/>
+      <c r="AMB8" s="1"/>
+      <c r="AMC8" s="1"/>
+      <c r="AMD8" s="1"/>
+      <c r="AME8" s="1"/>
+      <c r="AMF8" s="1"/>
+      <c r="AMG8" s="1"/>
+      <c r="AMH8" s="1"/>
+      <c r="AMI8" s="1"/>
+      <c r="AMJ8" s="1"/>
+      <c r="AMK8" s="1"/>
+      <c r="AML8" s="1"/>
+      <c r="AMM8" s="1"/>
+      <c r="AMN8" s="1"/>
+    </row>
+    <row r="9" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AKV9" s="0"/>
-      <c r="AKW9" s="0"/>
-      <c r="AKX9" s="0"/>
-      <c r="AKY9" s="0"/>
-      <c r="AKZ9" s="0"/>
-      <c r="ALA9" s="0"/>
-      <c r="ALB9" s="0"/>
-      <c r="ALC9" s="0"/>
-      <c r="ALD9" s="0"/>
-      <c r="ALE9" s="0"/>
-      <c r="ALF9" s="0"/>
-      <c r="ALG9" s="0"/>
-      <c r="ALH9" s="0"/>
-      <c r="ALI9" s="0"/>
-      <c r="ALJ9" s="0"/>
-      <c r="ALK9" s="0"/>
-      <c r="ALL9" s="0"/>
-      <c r="ALM9" s="0"/>
-      <c r="ALN9" s="0"/>
-      <c r="ALO9" s="0"/>
-      <c r="ALP9" s="0"/>
-      <c r="ALQ9" s="0"/>
-      <c r="ALR9" s="0"/>
-      <c r="ALS9" s="0"/>
-      <c r="ALT9" s="0"/>
-      <c r="ALU9" s="0"/>
-      <c r="ALV9" s="0"/>
-      <c r="ALW9" s="0"/>
-      <c r="ALX9" s="0"/>
-      <c r="ALY9" s="0"/>
-      <c r="ALZ9" s="0"/>
-      <c r="AMA9" s="0"/>
-      <c r="AMB9" s="0"/>
-      <c r="AMC9" s="0"/>
-      <c r="AMD9" s="0"/>
-      <c r="AME9" s="0"/>
-      <c r="AMF9" s="0"/>
-      <c r="AMG9" s="0"/>
-      <c r="AMH9" s="0"/>
-      <c r="AMI9" s="0"/>
-      <c r="AMJ9" s="0"/>
-      <c r="AMK9" s="0"/>
-      <c r="AML9" s="0"/>
-      <c r="AMM9" s="0"/>
-    </row>
-    <row r="10" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AKV10" s="0"/>
-      <c r="AKW10" s="0"/>
-      <c r="AKX10" s="0"/>
-      <c r="AKY10" s="0"/>
-      <c r="AKZ10" s="0"/>
-      <c r="ALA10" s="0"/>
-      <c r="ALB10" s="0"/>
-      <c r="ALC10" s="0"/>
-      <c r="ALD10" s="0"/>
-      <c r="ALE10" s="0"/>
-      <c r="ALF10" s="0"/>
-      <c r="ALG10" s="0"/>
-      <c r="ALH10" s="0"/>
-      <c r="ALI10" s="0"/>
-      <c r="ALJ10" s="0"/>
-      <c r="ALK10" s="0"/>
-      <c r="ALL10" s="0"/>
-      <c r="ALM10" s="0"/>
-      <c r="ALN10" s="0"/>
-      <c r="ALO10" s="0"/>
-      <c r="ALP10" s="0"/>
-      <c r="ALQ10" s="0"/>
-      <c r="ALR10" s="0"/>
-      <c r="ALS10" s="0"/>
-      <c r="ALT10" s="0"/>
-      <c r="ALU10" s="0"/>
-      <c r="ALV10" s="0"/>
-      <c r="ALW10" s="0"/>
-      <c r="ALX10" s="0"/>
-      <c r="ALY10" s="0"/>
-      <c r="ALZ10" s="0"/>
-      <c r="AMA10" s="0"/>
-      <c r="AMB10" s="0"/>
-      <c r="AMC10" s="0"/>
-      <c r="AMD10" s="0"/>
-      <c r="AME10" s="0"/>
-      <c r="AMF10" s="0"/>
-      <c r="AMG10" s="0"/>
-      <c r="AMH10" s="0"/>
-      <c r="AMI10" s="0"/>
-      <c r="AMJ10" s="0"/>
-      <c r="AMK10" s="0"/>
-      <c r="AML10" s="0"/>
-      <c r="AMM10" s="0"/>
-    </row>
-    <row r="11" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AKV12" s="1"/>
+      <c r="AKW12" s="1"/>
+      <c r="AKX12" s="1"/>
+      <c r="AKY12" s="1"/>
+      <c r="AKZ12" s="1"/>
+      <c r="ALA12" s="1"/>
+      <c r="ALB12" s="1"/>
+      <c r="ALC12" s="1"/>
+      <c r="ALD12" s="1"/>
+      <c r="ALE12" s="1"/>
+      <c r="ALF12" s="1"/>
+      <c r="ALG12" s="1"/>
+      <c r="ALH12" s="1"/>
+      <c r="ALI12" s="1"/>
+      <c r="ALJ12" s="1"/>
+      <c r="ALK12" s="1"/>
+      <c r="ALL12" s="1"/>
+      <c r="ALM12" s="1"/>
+      <c r="ALN12" s="1"/>
+      <c r="ALO12" s="1"/>
+      <c r="ALP12" s="1"/>
+      <c r="ALQ12" s="1"/>
+      <c r="ALR12" s="1"/>
+      <c r="ALS12" s="1"/>
+      <c r="ALT12" s="1"/>
+      <c r="ALU12" s="1"/>
+      <c r="ALV12" s="1"/>
+      <c r="ALW12" s="1"/>
+      <c r="ALX12" s="1"/>
+      <c r="ALY12" s="1"/>
+      <c r="ALZ12" s="1"/>
+      <c r="AMA12" s="1"/>
+      <c r="AMB12" s="1"/>
+      <c r="AMC12" s="1"/>
+      <c r="AMD12" s="1"/>
+      <c r="AME12" s="1"/>
+      <c r="AMF12" s="1"/>
+      <c r="AMG12" s="1"/>
+      <c r="AMH12" s="1"/>
+      <c r="AMI12" s="1"/>
+      <c r="AMJ12" s="1"/>
+      <c r="AMK12" s="1"/>
+      <c r="AML12" s="1"/>
+      <c r="AMM12" s="1"/>
+      <c r="AMN12" s="1"/>
+    </row>
+    <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AKV15" s="1"/>
+      <c r="AKW15" s="1"/>
+      <c r="AKX15" s="1"/>
+      <c r="AKY15" s="1"/>
+      <c r="AKZ15" s="1"/>
+      <c r="ALA15" s="1"/>
+      <c r="ALB15" s="1"/>
+      <c r="ALC15" s="1"/>
+      <c r="ALD15" s="1"/>
+      <c r="ALE15" s="1"/>
+      <c r="ALF15" s="1"/>
+      <c r="ALG15" s="1"/>
+      <c r="ALH15" s="1"/>
+      <c r="ALI15" s="1"/>
+      <c r="ALJ15" s="1"/>
+      <c r="ALK15" s="1"/>
+      <c r="ALL15" s="1"/>
+      <c r="ALM15" s="1"/>
+      <c r="ALN15" s="1"/>
+      <c r="ALO15" s="1"/>
+      <c r="ALP15" s="1"/>
+      <c r="ALQ15" s="1"/>
+      <c r="ALR15" s="1"/>
+      <c r="ALS15" s="1"/>
+      <c r="ALT15" s="1"/>
+      <c r="ALU15" s="1"/>
+      <c r="ALV15" s="1"/>
+      <c r="ALW15" s="1"/>
+      <c r="ALX15" s="1"/>
+      <c r="ALY15" s="1"/>
+      <c r="ALZ15" s="1"/>
+      <c r="AMA15" s="1"/>
+      <c r="AMB15" s="1"/>
+      <c r="AMC15" s="1"/>
+      <c r="AMD15" s="1"/>
+      <c r="AME15" s="1"/>
+      <c r="AMF15" s="1"/>
+      <c r="AMG15" s="1"/>
+      <c r="AMH15" s="1"/>
+      <c r="AMI15" s="1"/>
+      <c r="AMJ15" s="1"/>
+      <c r="AMK15" s="1"/>
+      <c r="AML15" s="1"/>
+      <c r="AMM15" s="1"/>
+      <c r="AMN15" s="1"/>
+    </row>
+    <row r="16" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AKV18" s="1"/>
+      <c r="AKW18" s="1"/>
+      <c r="AKX18" s="1"/>
+      <c r="AKY18" s="1"/>
+      <c r="AKZ18" s="1"/>
+      <c r="ALA18" s="1"/>
+      <c r="ALB18" s="1"/>
+      <c r="ALC18" s="1"/>
+      <c r="ALD18" s="1"/>
+      <c r="ALE18" s="1"/>
+      <c r="ALF18" s="1"/>
+      <c r="ALG18" s="1"/>
+      <c r="ALH18" s="1"/>
+      <c r="ALI18" s="1"/>
+      <c r="ALJ18" s="1"/>
+      <c r="ALK18" s="1"/>
+      <c r="ALL18" s="1"/>
+      <c r="ALM18" s="1"/>
+      <c r="ALN18" s="1"/>
+      <c r="ALO18" s="1"/>
+      <c r="ALP18" s="1"/>
+      <c r="ALQ18" s="1"/>
+      <c r="ALR18" s="1"/>
+      <c r="ALS18" s="1"/>
+      <c r="ALT18" s="1"/>
+      <c r="ALU18" s="1"/>
+      <c r="ALV18" s="1"/>
+      <c r="ALW18" s="1"/>
+      <c r="ALX18" s="1"/>
+      <c r="ALY18" s="1"/>
+      <c r="ALZ18" s="1"/>
+      <c r="AMA18" s="1"/>
+      <c r="AMB18" s="1"/>
+      <c r="AMC18" s="1"/>
+      <c r="AMD18" s="1"/>
+      <c r="AME18" s="1"/>
+      <c r="AMF18" s="1"/>
+      <c r="AMG18" s="1"/>
+      <c r="AMH18" s="1"/>
+      <c r="AMI18" s="1"/>
+      <c r="AMJ18" s="1"/>
+      <c r="AMK18" s="1"/>
+      <c r="AML18" s="1"/>
+      <c r="AMM18" s="1"/>
+      <c r="AMN18" s="1"/>
+    </row>
+    <row r="19" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AKV19" s="1"/>
+      <c r="AKW19" s="1"/>
+      <c r="AKX19" s="1"/>
+      <c r="AKY19" s="1"/>
+      <c r="AKZ19" s="1"/>
+      <c r="ALA19" s="1"/>
+      <c r="ALB19" s="1"/>
+      <c r="ALC19" s="1"/>
+      <c r="ALD19" s="1"/>
+      <c r="ALE19" s="1"/>
+      <c r="ALF19" s="1"/>
+      <c r="ALG19" s="1"/>
+      <c r="ALH19" s="1"/>
+      <c r="ALI19" s="1"/>
+      <c r="ALJ19" s="1"/>
+      <c r="ALK19" s="1"/>
+      <c r="ALL19" s="1"/>
+      <c r="ALM19" s="1"/>
+      <c r="ALN19" s="1"/>
+      <c r="ALO19" s="1"/>
+      <c r="ALP19" s="1"/>
+      <c r="ALQ19" s="1"/>
+      <c r="ALR19" s="1"/>
+      <c r="ALS19" s="1"/>
+      <c r="ALT19" s="1"/>
+      <c r="ALU19" s="1"/>
+      <c r="ALV19" s="1"/>
+      <c r="ALW19" s="1"/>
+      <c r="ALX19" s="1"/>
+      <c r="ALY19" s="1"/>
+      <c r="ALZ19" s="1"/>
+      <c r="AMA19" s="1"/>
+      <c r="AMB19" s="1"/>
+      <c r="AMC19" s="1"/>
+      <c r="AMD19" s="1"/>
+      <c r="AME19" s="1"/>
+      <c r="AMF19" s="1"/>
+      <c r="AMG19" s="1"/>
+      <c r="AMH19" s="1"/>
+      <c r="AMI19" s="1"/>
+      <c r="AMJ19" s="1"/>
+      <c r="AMK19" s="1"/>
+      <c r="AML19" s="1"/>
+      <c r="AMM19" s="1"/>
+      <c r="AMN19" s="1"/>
+    </row>
+    <row r="20" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AKV11" s="0"/>
-      <c r="AKW11" s="0"/>
-      <c r="AKX11" s="0"/>
-      <c r="AKY11" s="0"/>
-      <c r="AKZ11" s="0"/>
-      <c r="ALA11" s="0"/>
-      <c r="ALB11" s="0"/>
-      <c r="ALC11" s="0"/>
-      <c r="ALD11" s="0"/>
-      <c r="ALE11" s="0"/>
-      <c r="ALF11" s="0"/>
-      <c r="ALG11" s="0"/>
-      <c r="ALH11" s="0"/>
-      <c r="ALI11" s="0"/>
-      <c r="ALJ11" s="0"/>
-      <c r="ALK11" s="0"/>
-      <c r="ALL11" s="0"/>
-      <c r="ALM11" s="0"/>
-      <c r="ALN11" s="0"/>
-      <c r="ALO11" s="0"/>
-      <c r="ALP11" s="0"/>
-      <c r="ALQ11" s="0"/>
-      <c r="ALR11" s="0"/>
-      <c r="ALS11" s="0"/>
-      <c r="ALT11" s="0"/>
-      <c r="ALU11" s="0"/>
-      <c r="ALV11" s="0"/>
-      <c r="ALW11" s="0"/>
-      <c r="ALX11" s="0"/>
-      <c r="ALY11" s="0"/>
-      <c r="ALZ11" s="0"/>
-      <c r="AMA11" s="0"/>
-      <c r="AMB11" s="0"/>
-      <c r="AMC11" s="0"/>
-      <c r="AMD11" s="0"/>
-      <c r="AME11" s="0"/>
-      <c r="AMF11" s="0"/>
-      <c r="AMG11" s="0"/>
-      <c r="AMH11" s="0"/>
-      <c r="AMI11" s="0"/>
-      <c r="AMJ11" s="0"/>
-      <c r="AMK11" s="0"/>
-      <c r="AML11" s="0"/>
-      <c r="AMM11" s="0"/>
-    </row>
-    <row r="12" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="AKU12" s="1"/>
-      <c r="AKV12" s="0"/>
-      <c r="AKW12" s="0"/>
-      <c r="AKX12" s="0"/>
-      <c r="AKY12" s="0"/>
-      <c r="AKZ12" s="0"/>
-      <c r="ALA12" s="0"/>
-      <c r="ALB12" s="0"/>
-      <c r="ALC12" s="0"/>
-      <c r="ALD12" s="0"/>
-      <c r="ALE12" s="0"/>
-      <c r="ALF12" s="0"/>
-      <c r="ALG12" s="0"/>
-      <c r="ALH12" s="0"/>
-      <c r="ALI12" s="0"/>
-      <c r="ALJ12" s="0"/>
-      <c r="ALK12" s="0"/>
-      <c r="ALL12" s="0"/>
-      <c r="ALM12" s="0"/>
-      <c r="ALN12" s="0"/>
-      <c r="ALO12" s="0"/>
-      <c r="ALP12" s="0"/>
-      <c r="ALQ12" s="0"/>
-      <c r="ALR12" s="0"/>
-      <c r="ALS12" s="0"/>
-      <c r="ALT12" s="0"/>
-      <c r="ALU12" s="0"/>
-      <c r="ALV12" s="0"/>
-      <c r="ALW12" s="0"/>
-      <c r="ALX12" s="0"/>
-      <c r="ALY12" s="0"/>
-      <c r="ALZ12" s="0"/>
-      <c r="AMA12" s="0"/>
-      <c r="AMB12" s="0"/>
-      <c r="AMC12" s="0"/>
-      <c r="AMD12" s="0"/>
-      <c r="AME12" s="0"/>
-      <c r="AMF12" s="0"/>
-      <c r="AMG12" s="0"/>
-      <c r="AMH12" s="0"/>
-      <c r="AMI12" s="0"/>
-      <c r="AMJ12" s="0"/>
-      <c r="AMK12" s="0"/>
-      <c r="AML12" s="0"/>
-      <c r="AMM12" s="0"/>
-    </row>
-    <row r="13" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+      <c r="B20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AKV13" s="0"/>
-      <c r="AKW13" s="0"/>
-      <c r="AKX13" s="0"/>
-      <c r="AKY13" s="0"/>
-      <c r="AKZ13" s="0"/>
-      <c r="ALA13" s="0"/>
-      <c r="ALB13" s="0"/>
-      <c r="ALC13" s="0"/>
-      <c r="ALD13" s="0"/>
-      <c r="ALE13" s="0"/>
-      <c r="ALF13" s="0"/>
-      <c r="ALG13" s="0"/>
-      <c r="ALH13" s="0"/>
-      <c r="ALI13" s="0"/>
-      <c r="ALJ13" s="0"/>
-      <c r="ALK13" s="0"/>
-      <c r="ALL13" s="0"/>
-      <c r="ALM13" s="0"/>
-      <c r="ALN13" s="0"/>
-      <c r="ALO13" s="0"/>
-      <c r="ALP13" s="0"/>
-      <c r="ALQ13" s="0"/>
-      <c r="ALR13" s="0"/>
-      <c r="ALS13" s="0"/>
-      <c r="ALT13" s="0"/>
-      <c r="ALU13" s="0"/>
-      <c r="ALV13" s="0"/>
-      <c r="ALW13" s="0"/>
-      <c r="ALX13" s="0"/>
-      <c r="ALY13" s="0"/>
-      <c r="ALZ13" s="0"/>
-      <c r="AMA13" s="0"/>
-      <c r="AMB13" s="0"/>
-      <c r="AMC13" s="0"/>
-      <c r="AMD13" s="0"/>
-      <c r="AME13" s="0"/>
-      <c r="AMF13" s="0"/>
-      <c r="AMG13" s="0"/>
-      <c r="AMH13" s="0"/>
-      <c r="AMI13" s="0"/>
-      <c r="AMJ13" s="0"/>
-      <c r="AMK13" s="0"/>
-      <c r="AML13" s="0"/>
-      <c r="AMM13" s="0"/>
-    </row>
-    <row r="14" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+      <c r="B21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AKV14" s="0"/>
-      <c r="AKW14" s="0"/>
-      <c r="AKX14" s="0"/>
-      <c r="AKY14" s="0"/>
-      <c r="AKZ14" s="0"/>
-      <c r="ALA14" s="0"/>
-      <c r="ALB14" s="0"/>
-      <c r="ALC14" s="0"/>
-      <c r="ALD14" s="0"/>
-      <c r="ALE14" s="0"/>
-      <c r="ALF14" s="0"/>
-      <c r="ALG14" s="0"/>
-      <c r="ALH14" s="0"/>
-      <c r="ALI14" s="0"/>
-      <c r="ALJ14" s="0"/>
-      <c r="ALK14" s="0"/>
-      <c r="ALL14" s="0"/>
-      <c r="ALM14" s="0"/>
-      <c r="ALN14" s="0"/>
-      <c r="ALO14" s="0"/>
-      <c r="ALP14" s="0"/>
-      <c r="ALQ14" s="0"/>
-      <c r="ALR14" s="0"/>
-      <c r="ALS14" s="0"/>
-      <c r="ALT14" s="0"/>
-      <c r="ALU14" s="0"/>
-      <c r="ALV14" s="0"/>
-      <c r="ALW14" s="0"/>
-      <c r="ALX14" s="0"/>
-      <c r="ALY14" s="0"/>
-      <c r="ALZ14" s="0"/>
-      <c r="AMA14" s="0"/>
-      <c r="AMB14" s="0"/>
-      <c r="AMC14" s="0"/>
-      <c r="AMD14" s="0"/>
-      <c r="AME14" s="0"/>
-      <c r="AMF14" s="0"/>
-      <c r="AMG14" s="0"/>
-      <c r="AMH14" s="0"/>
-      <c r="AMI14" s="0"/>
-      <c r="AMJ14" s="0"/>
-      <c r="AMK14" s="0"/>
-      <c r="AML14" s="0"/>
-      <c r="AMM14" s="0"/>
-    </row>
-    <row r="15" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AKU15" s="1"/>
-      <c r="AKV15" s="0"/>
-      <c r="AKW15" s="0"/>
-      <c r="AKX15" s="0"/>
-      <c r="AKY15" s="0"/>
-      <c r="AKZ15" s="0"/>
-      <c r="ALA15" s="0"/>
-      <c r="ALB15" s="0"/>
-      <c r="ALC15" s="0"/>
-      <c r="ALD15" s="0"/>
-      <c r="ALE15" s="0"/>
-      <c r="ALF15" s="0"/>
-      <c r="ALG15" s="0"/>
-      <c r="ALH15" s="0"/>
-      <c r="ALI15" s="0"/>
-      <c r="ALJ15" s="0"/>
-      <c r="ALK15" s="0"/>
-      <c r="ALL15" s="0"/>
-      <c r="ALM15" s="0"/>
-      <c r="ALN15" s="0"/>
-      <c r="ALO15" s="0"/>
-      <c r="ALP15" s="0"/>
-      <c r="ALQ15" s="0"/>
-      <c r="ALR15" s="0"/>
-      <c r="ALS15" s="0"/>
-      <c r="ALT15" s="0"/>
-      <c r="ALU15" s="0"/>
-      <c r="ALV15" s="0"/>
-      <c r="ALW15" s="0"/>
-      <c r="ALX15" s="0"/>
-      <c r="ALY15" s="0"/>
-      <c r="ALZ15" s="0"/>
-      <c r="AMA15" s="0"/>
-      <c r="AMB15" s="0"/>
-      <c r="AMC15" s="0"/>
-      <c r="AMD15" s="0"/>
-      <c r="AME15" s="0"/>
-      <c r="AMF15" s="0"/>
-      <c r="AMG15" s="0"/>
-      <c r="AMH15" s="0"/>
-      <c r="AMI15" s="0"/>
-      <c r="AMJ15" s="0"/>
-      <c r="AMK15" s="0"/>
-      <c r="AML15" s="0"/>
-      <c r="AMM15" s="0"/>
-    </row>
-    <row r="16" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="AKV16" s="0"/>
-      <c r="AKW16" s="0"/>
-      <c r="AKX16" s="0"/>
-      <c r="AKY16" s="0"/>
-      <c r="AKZ16" s="0"/>
-      <c r="ALA16" s="0"/>
-      <c r="ALB16" s="0"/>
-      <c r="ALC16" s="0"/>
-      <c r="ALD16" s="0"/>
-      <c r="ALE16" s="0"/>
-      <c r="ALF16" s="0"/>
-      <c r="ALG16" s="0"/>
-      <c r="ALH16" s="0"/>
-      <c r="ALI16" s="0"/>
-      <c r="ALJ16" s="0"/>
-      <c r="ALK16" s="0"/>
-      <c r="ALL16" s="0"/>
-      <c r="ALM16" s="0"/>
-      <c r="ALN16" s="0"/>
-      <c r="ALO16" s="0"/>
-      <c r="ALP16" s="0"/>
-      <c r="ALQ16" s="0"/>
-      <c r="ALR16" s="0"/>
-      <c r="ALS16" s="0"/>
-      <c r="ALT16" s="0"/>
-      <c r="ALU16" s="0"/>
-      <c r="ALV16" s="0"/>
-      <c r="ALW16" s="0"/>
-      <c r="ALX16" s="0"/>
-      <c r="ALY16" s="0"/>
-      <c r="ALZ16" s="0"/>
-      <c r="AMA16" s="0"/>
-      <c r="AMB16" s="0"/>
-      <c r="AMC16" s="0"/>
-      <c r="AMD16" s="0"/>
-      <c r="AME16" s="0"/>
-      <c r="AMF16" s="0"/>
-      <c r="AMG16" s="0"/>
-      <c r="AMH16" s="0"/>
-      <c r="AMI16" s="0"/>
-      <c r="AMJ16" s="0"/>
-      <c r="AMK16" s="0"/>
-      <c r="AML16" s="0"/>
-      <c r="AMM16" s="0"/>
-    </row>
-    <row r="17" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="AKV17" s="0"/>
-      <c r="AKW17" s="0"/>
-      <c r="AKX17" s="0"/>
-      <c r="AKY17" s="0"/>
-      <c r="AKZ17" s="0"/>
-      <c r="ALA17" s="0"/>
-      <c r="ALB17" s="0"/>
-      <c r="ALC17" s="0"/>
-      <c r="ALD17" s="0"/>
-      <c r="ALE17" s="0"/>
-      <c r="ALF17" s="0"/>
-      <c r="ALG17" s="0"/>
-      <c r="ALH17" s="0"/>
-      <c r="ALI17" s="0"/>
-      <c r="ALJ17" s="0"/>
-      <c r="ALK17" s="0"/>
-      <c r="ALL17" s="0"/>
-      <c r="ALM17" s="0"/>
-      <c r="ALN17" s="0"/>
-      <c r="ALO17" s="0"/>
-      <c r="ALP17" s="0"/>
-      <c r="ALQ17" s="0"/>
-      <c r="ALR17" s="0"/>
-      <c r="ALS17" s="0"/>
-      <c r="ALT17" s="0"/>
-      <c r="ALU17" s="0"/>
-      <c r="ALV17" s="0"/>
-      <c r="ALW17" s="0"/>
-      <c r="ALX17" s="0"/>
-      <c r="ALY17" s="0"/>
-      <c r="ALZ17" s="0"/>
-      <c r="AMA17" s="0"/>
-      <c r="AMB17" s="0"/>
-      <c r="AMC17" s="0"/>
-      <c r="AMD17" s="0"/>
-      <c r="AME17" s="0"/>
-      <c r="AMF17" s="0"/>
-      <c r="AMG17" s="0"/>
-      <c r="AMH17" s="0"/>
-      <c r="AMI17" s="0"/>
-      <c r="AMJ17" s="0"/>
-      <c r="AMK17" s="0"/>
-      <c r="AML17" s="0"/>
-      <c r="AMM17" s="0"/>
-    </row>
-    <row r="18" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="AKU18" s="1"/>
-      <c r="AKV18" s="0"/>
-      <c r="AKW18" s="0"/>
-      <c r="AKX18" s="0"/>
-      <c r="AKY18" s="0"/>
-      <c r="AKZ18" s="0"/>
-      <c r="ALA18" s="0"/>
-      <c r="ALB18" s="0"/>
-      <c r="ALC18" s="0"/>
-      <c r="ALD18" s="0"/>
-      <c r="ALE18" s="0"/>
-      <c r="ALF18" s="0"/>
-      <c r="ALG18" s="0"/>
-      <c r="ALH18" s="0"/>
-      <c r="ALI18" s="0"/>
-      <c r="ALJ18" s="0"/>
-      <c r="ALK18" s="0"/>
-      <c r="ALL18" s="0"/>
-      <c r="ALM18" s="0"/>
-      <c r="ALN18" s="0"/>
-      <c r="ALO18" s="0"/>
-      <c r="ALP18" s="0"/>
-      <c r="ALQ18" s="0"/>
-      <c r="ALR18" s="0"/>
-      <c r="ALS18" s="0"/>
-      <c r="ALT18" s="0"/>
-      <c r="ALU18" s="0"/>
-      <c r="ALV18" s="0"/>
-      <c r="ALW18" s="0"/>
-      <c r="ALX18" s="0"/>
-      <c r="ALY18" s="0"/>
-      <c r="ALZ18" s="0"/>
-      <c r="AMA18" s="0"/>
-      <c r="AMB18" s="0"/>
-      <c r="AMC18" s="0"/>
-      <c r="AMD18" s="0"/>
-      <c r="AME18" s="0"/>
-      <c r="AMF18" s="0"/>
-      <c r="AMG18" s="0"/>
-      <c r="AMH18" s="0"/>
-      <c r="AMI18" s="0"/>
-      <c r="AMJ18" s="0"/>
-      <c r="AMK18" s="0"/>
-      <c r="AML18" s="0"/>
-      <c r="AMM18" s="0"/>
-    </row>
-    <row r="19" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="AKU19" s="1"/>
-      <c r="AKV19" s="0"/>
-      <c r="AKW19" s="0"/>
-      <c r="AKX19" s="0"/>
-      <c r="AKY19" s="0"/>
-      <c r="AKZ19" s="0"/>
-      <c r="ALA19" s="0"/>
-      <c r="ALB19" s="0"/>
-      <c r="ALC19" s="0"/>
-      <c r="ALD19" s="0"/>
-      <c r="ALE19" s="0"/>
-      <c r="ALF19" s="0"/>
-      <c r="ALG19" s="0"/>
-      <c r="ALH19" s="0"/>
-      <c r="ALI19" s="0"/>
-      <c r="ALJ19" s="0"/>
-      <c r="ALK19" s="0"/>
-      <c r="ALL19" s="0"/>
-      <c r="ALM19" s="0"/>
-      <c r="ALN19" s="0"/>
-      <c r="ALO19" s="0"/>
-      <c r="ALP19" s="0"/>
-      <c r="ALQ19" s="0"/>
-      <c r="ALR19" s="0"/>
-      <c r="ALS19" s="0"/>
-      <c r="ALT19" s="0"/>
-      <c r="ALU19" s="0"/>
-      <c r="ALV19" s="0"/>
-      <c r="ALW19" s="0"/>
-      <c r="ALX19" s="0"/>
-      <c r="ALY19" s="0"/>
-      <c r="ALZ19" s="0"/>
-      <c r="AMA19" s="0"/>
-      <c r="AMB19" s="0"/>
-      <c r="AMC19" s="0"/>
-      <c r="AMD19" s="0"/>
-      <c r="AME19" s="0"/>
-      <c r="AMF19" s="0"/>
-      <c r="AMG19" s="0"/>
-      <c r="AMH19" s="0"/>
-      <c r="AMI19" s="0"/>
-      <c r="AMJ19" s="0"/>
-      <c r="AMK19" s="0"/>
-      <c r="AML19" s="0"/>
-      <c r="AMM19" s="0"/>
-    </row>
-    <row r="20" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="AKV20" s="0"/>
-      <c r="AKW20" s="0"/>
-      <c r="AKX20" s="0"/>
-      <c r="AKY20" s="0"/>
-      <c r="AKZ20" s="0"/>
-      <c r="ALA20" s="0"/>
-      <c r="ALB20" s="0"/>
-      <c r="ALC20" s="0"/>
-      <c r="ALD20" s="0"/>
-      <c r="ALE20" s="0"/>
-      <c r="ALF20" s="0"/>
-      <c r="ALG20" s="0"/>
-      <c r="ALH20" s="0"/>
-      <c r="ALI20" s="0"/>
-      <c r="ALJ20" s="0"/>
-      <c r="ALK20" s="0"/>
-      <c r="ALL20" s="0"/>
-      <c r="ALM20" s="0"/>
-      <c r="ALN20" s="0"/>
-      <c r="ALO20" s="0"/>
-      <c r="ALP20" s="0"/>
-      <c r="ALQ20" s="0"/>
-      <c r="ALR20" s="0"/>
-      <c r="ALS20" s="0"/>
-      <c r="ALT20" s="0"/>
-      <c r="ALU20" s="0"/>
-      <c r="ALV20" s="0"/>
-      <c r="ALW20" s="0"/>
-      <c r="ALX20" s="0"/>
-      <c r="ALY20" s="0"/>
-      <c r="ALZ20" s="0"/>
-      <c r="AMA20" s="0"/>
-      <c r="AMB20" s="0"/>
-      <c r="AMC20" s="0"/>
-      <c r="AMD20" s="0"/>
-      <c r="AME20" s="0"/>
-      <c r="AMF20" s="0"/>
-      <c r="AMG20" s="0"/>
-      <c r="AMH20" s="0"/>
-      <c r="AMI20" s="0"/>
-      <c r="AMJ20" s="0"/>
-      <c r="AMK20" s="0"/>
-      <c r="AML20" s="0"/>
-      <c r="AMM20" s="0"/>
-    </row>
-    <row r="21" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="AKV21" s="0"/>
-      <c r="AKW21" s="0"/>
-      <c r="AKX21" s="0"/>
-      <c r="AKY21" s="0"/>
-      <c r="AKZ21" s="0"/>
-      <c r="ALA21" s="0"/>
-      <c r="ALB21" s="0"/>
-      <c r="ALC21" s="0"/>
-      <c r="ALD21" s="0"/>
-      <c r="ALE21" s="0"/>
-      <c r="ALF21" s="0"/>
-      <c r="ALG21" s="0"/>
-      <c r="ALH21" s="0"/>
-      <c r="ALI21" s="0"/>
-      <c r="ALJ21" s="0"/>
-      <c r="ALK21" s="0"/>
-      <c r="ALL21" s="0"/>
-      <c r="ALM21" s="0"/>
-      <c r="ALN21" s="0"/>
-      <c r="ALO21" s="0"/>
-      <c r="ALP21" s="0"/>
-      <c r="ALQ21" s="0"/>
-      <c r="ALR21" s="0"/>
-      <c r="ALS21" s="0"/>
-      <c r="ALT21" s="0"/>
-      <c r="ALU21" s="0"/>
-      <c r="ALV21" s="0"/>
-      <c r="ALW21" s="0"/>
-      <c r="ALX21" s="0"/>
-      <c r="ALY21" s="0"/>
-      <c r="ALZ21" s="0"/>
-      <c r="AMA21" s="0"/>
-      <c r="AMB21" s="0"/>
-      <c r="AMC21" s="0"/>
-      <c r="AMD21" s="0"/>
-      <c r="AME21" s="0"/>
-      <c r="AMF21" s="0"/>
-      <c r="AMG21" s="0"/>
-      <c r="AMH21" s="0"/>
-      <c r="AMI21" s="0"/>
-      <c r="AMJ21" s="0"/>
-      <c r="AMK21" s="0"/>
-      <c r="AML21" s="0"/>
-      <c r="AMM21" s="0"/>
-    </row>
-    <row r="22" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>9</v>
-      </c>
       <c r="B22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>5</v>
+        <v>62</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>100</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -5669,60 +5963,61 @@
       <c r="AKS22" s="1"/>
       <c r="AKT22" s="1"/>
       <c r="AKU22" s="1"/>
-      <c r="AKV22" s="0"/>
-      <c r="AKW22" s="0"/>
-      <c r="AKX22" s="0"/>
-      <c r="AKY22" s="0"/>
-      <c r="AKZ22" s="0"/>
-      <c r="ALA22" s="0"/>
-      <c r="ALB22" s="0"/>
-      <c r="ALC22" s="0"/>
-      <c r="ALD22" s="0"/>
-      <c r="ALE22" s="0"/>
-      <c r="ALF22" s="0"/>
-      <c r="ALG22" s="0"/>
-      <c r="ALH22" s="0"/>
-      <c r="ALI22" s="0"/>
-      <c r="ALJ22" s="0"/>
-      <c r="ALK22" s="0"/>
-      <c r="ALL22" s="0"/>
-      <c r="ALM22" s="0"/>
-      <c r="ALN22" s="0"/>
-      <c r="ALO22" s="0"/>
-      <c r="ALP22" s="0"/>
-      <c r="ALQ22" s="0"/>
-      <c r="ALR22" s="0"/>
-      <c r="ALS22" s="0"/>
-      <c r="ALT22" s="0"/>
-      <c r="ALU22" s="0"/>
-      <c r="ALV22" s="0"/>
-      <c r="ALW22" s="0"/>
-      <c r="ALX22" s="0"/>
-      <c r="ALY22" s="0"/>
-      <c r="ALZ22" s="0"/>
-      <c r="AMA22" s="0"/>
-      <c r="AMB22" s="0"/>
-      <c r="AMC22" s="0"/>
-      <c r="AMD22" s="0"/>
-      <c r="AME22" s="0"/>
-      <c r="AMF22" s="0"/>
-      <c r="AMG22" s="0"/>
-      <c r="AMH22" s="0"/>
-      <c r="AMI22" s="0"/>
-      <c r="AMJ22" s="0"/>
-      <c r="AMK22" s="0"/>
-      <c r="AML22" s="0"/>
-      <c r="AMM22" s="0"/>
-    </row>
-    <row r="23" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AKV22" s="1"/>
+      <c r="AKW22" s="1"/>
+      <c r="AKX22" s="1"/>
+      <c r="AKY22" s="1"/>
+      <c r="AKZ22" s="1"/>
+      <c r="ALA22" s="1"/>
+      <c r="ALB22" s="1"/>
+      <c r="ALC22" s="1"/>
+      <c r="ALD22" s="1"/>
+      <c r="ALE22" s="1"/>
+      <c r="ALF22" s="1"/>
+      <c r="ALG22" s="1"/>
+      <c r="ALH22" s="1"/>
+      <c r="ALI22" s="1"/>
+      <c r="ALJ22" s="1"/>
+      <c r="ALK22" s="1"/>
+      <c r="ALL22" s="1"/>
+      <c r="ALM22" s="1"/>
+      <c r="ALN22" s="1"/>
+      <c r="ALO22" s="1"/>
+      <c r="ALP22" s="1"/>
+      <c r="ALQ22" s="1"/>
+      <c r="ALR22" s="1"/>
+      <c r="ALS22" s="1"/>
+      <c r="ALT22" s="1"/>
+      <c r="ALU22" s="1"/>
+      <c r="ALV22" s="1"/>
+      <c r="ALW22" s="1"/>
+      <c r="ALX22" s="1"/>
+      <c r="ALY22" s="1"/>
+      <c r="ALZ22" s="1"/>
+      <c r="AMA22" s="1"/>
+      <c r="AMB22" s="1"/>
+      <c r="AMC22" s="1"/>
+      <c r="AMD22" s="1"/>
+      <c r="AME22" s="1"/>
+      <c r="AMF22" s="1"/>
+      <c r="AMG22" s="1"/>
+      <c r="AMH22" s="1"/>
+      <c r="AMI22" s="1"/>
+      <c r="AMJ22" s="1"/>
+      <c r="AMK22" s="1"/>
+      <c r="AML22" s="1"/>
+      <c r="AMM22" s="1"/>
+      <c r="AMN22" s="1"/>
+    </row>
+    <row r="23" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>5</v>
+        <v>74</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>100</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -6703,52 +6998,8 @@
       <c r="AKR23" s="2"/>
       <c r="AKS23" s="2"/>
       <c r="AKT23" s="2"/>
-      <c r="AKV23" s="0"/>
-      <c r="AKW23" s="0"/>
-      <c r="AKX23" s="0"/>
-      <c r="AKY23" s="0"/>
-      <c r="AKZ23" s="0"/>
-      <c r="ALA23" s="0"/>
-      <c r="ALB23" s="0"/>
-      <c r="ALC23" s="0"/>
-      <c r="ALD23" s="0"/>
-      <c r="ALE23" s="0"/>
-      <c r="ALF23" s="0"/>
-      <c r="ALG23" s="0"/>
-      <c r="ALH23" s="0"/>
-      <c r="ALI23" s="0"/>
-      <c r="ALJ23" s="0"/>
-      <c r="ALK23" s="0"/>
-      <c r="ALL23" s="0"/>
-      <c r="ALM23" s="0"/>
-      <c r="ALN23" s="0"/>
-      <c r="ALO23" s="0"/>
-      <c r="ALP23" s="0"/>
-      <c r="ALQ23" s="0"/>
-      <c r="ALR23" s="0"/>
-      <c r="ALS23" s="0"/>
-      <c r="ALT23" s="0"/>
-      <c r="ALU23" s="0"/>
-      <c r="ALV23" s="0"/>
-      <c r="ALW23" s="0"/>
-      <c r="ALX23" s="0"/>
-      <c r="ALY23" s="0"/>
-      <c r="ALZ23" s="0"/>
-      <c r="AMA23" s="0"/>
-      <c r="AMB23" s="0"/>
-      <c r="AMC23" s="0"/>
-      <c r="AMD23" s="0"/>
-      <c r="AME23" s="0"/>
-      <c r="AMF23" s="0"/>
-      <c r="AMG23" s="0"/>
-      <c r="AMH23" s="0"/>
-      <c r="AMI23" s="0"/>
-      <c r="AMJ23" s="0"/>
-      <c r="AMK23" s="0"/>
-      <c r="AML23" s="0"/>
-      <c r="AMM23" s="0"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="AKU23" s="2"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -6794,7 +7045,7 @@
         <v>45961</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6802,7 +7053,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>3</v>
@@ -6820,7 +7071,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0</v>
@@ -6841,7 +7092,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>3</v>
@@ -6856,7 +7107,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>4</v>
@@ -6874,7 +7125,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
@@ -6892,7 +7143,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0</v>
@@ -6910,7 +7161,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>3</v>
@@ -6928,7 +7179,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>4</v>
@@ -6949,7 +7200,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>3</v>
@@ -6964,7 +7215,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>3</v>
@@ -6979,7 +7230,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>3</v>
@@ -7000,7 +7251,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0</v>
@@ -7015,7 +7266,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>3</v>
@@ -7036,7 +7287,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>3</v>
@@ -7057,7 +7308,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>3</v>
@@ -7075,7 +7326,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>0</v>
@@ -7090,7 +7341,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>3</v>
@@ -7108,7 +7359,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>0</v>
@@ -7126,7 +7377,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>3</v>
@@ -7141,7 +7392,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>3</v>
@@ -7159,7 +7410,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>3</v>
@@ -7177,7 +7428,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>3</v>
@@ -7216,22 +7467,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7239,16 +7490,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -7262,16 +7513,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -7285,16 +7536,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -7308,16 +7559,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -7331,7 +7582,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -7345,7 +7596,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -7359,16 +7610,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -7382,16 +7633,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -7410,13 +7661,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -7427,16 +7678,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>10</v>
@@ -7450,7 +7701,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>1</v>
@@ -7464,16 +7715,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>10</v>
@@ -7487,16 +7738,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>7</v>
@@ -7510,16 +7761,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -7533,16 +7784,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>9</v>
@@ -7556,16 +7807,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>10</v>
@@ -7579,7 +7830,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -7593,16 +7844,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>10</v>
@@ -7616,16 +7867,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -7639,16 +7890,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>9</v>
@@ -7662,16 +7913,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>10</v>
@@ -7685,16 +7936,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>10</v>
@@ -7713,13 +7964,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>9</v>
@@ -7727,13 +7978,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>7</v>
@@ -7744,16 +7995,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>10</v>
@@ -7792,24 +8043,24 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>9</v>
@@ -7844,22 +8095,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7867,16 +8118,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>10</v>
@@ -7890,16 +8141,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -7913,16 +8164,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>8</v>
@@ -7936,16 +8187,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -7959,7 +8210,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -7973,7 +8224,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -7987,16 +8238,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -8010,16 +8261,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -8033,16 +8284,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -8056,7 +8307,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -8070,16 +8321,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -8093,16 +8344,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -8116,7 +8367,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1</v>
@@ -8130,16 +8381,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>10</v>
@@ -8153,16 +8404,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>10</v>
@@ -8176,7 +8427,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -8190,16 +8441,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>10</v>
@@ -8213,16 +8464,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>10</v>
@@ -8236,16 +8487,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>149</v>
+        <v>174</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>10</v>
@@ -8259,16 +8510,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -8282,16 +8533,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>153</v>
+        <v>178</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>10</v>
@@ -8310,13 +8561,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>9</v>
@@ -8324,13 +8575,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>8</v>
@@ -8338,13 +8589,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>6</v>
@@ -8352,13 +8603,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>5</v>
@@ -8369,16 +8620,16 @@
         <v>22</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>10</v>
@@ -8416,13 +8667,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8430,16 +8681,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>7</v>
@@ -8450,16 +8701,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>10</v>
@@ -8470,16 +8721,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>9</v>
@@ -8490,16 +8741,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>10</v>
@@ -8510,7 +8761,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -8521,7 +8772,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -8532,16 +8783,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -8552,16 +8803,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -8572,16 +8823,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>8</v>
@@ -8592,7 +8843,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -8603,16 +8854,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>10</v>
@@ -8623,16 +8874,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>9</v>
@@ -8643,16 +8894,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>7</v>
@@ -8663,16 +8914,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>7</v>
@@ -8683,16 +8934,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>7</v>
@@ -8703,7 +8954,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -8714,16 +8965,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>8</v>
@@ -8734,16 +8985,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>7</v>
@@ -8754,16 +9005,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>9</v>
@@ -8774,16 +9025,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>7</v>
@@ -8794,16 +9045,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>9</v>
@@ -8814,16 +9065,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>8</v>
@@ -8858,22 +9109,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8881,7 +9132,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -8892,16 +9143,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>9</v>
@@ -8912,7 +9163,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
@@ -8923,16 +9174,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>9</v>
@@ -8943,7 +9194,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
@@ -8954,7 +9205,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>1</v>
@@ -8965,16 +9216,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>10</v>
@@ -8985,16 +9236,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>10</v>
@@ -9005,16 +9256,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>10</v>
@@ -9025,7 +9276,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>1</v>
@@ -9036,16 +9287,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>7</v>
@@ -9056,16 +9307,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>7</v>
@@ -9076,7 +9327,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1</v>
@@ -9087,16 +9338,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>7</v>
@@ -9107,16 +9358,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
@@ -9127,7 +9378,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -9138,7 +9389,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -9149,7 +9400,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>1</v>
@@ -9160,16 +9411,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>1</v>
@@ -9180,7 +9431,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>1</v>
@@ -9191,16 +9442,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>10</v>
@@ -9208,13 +9459,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C23" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>6</v>
@@ -9225,7 +9476,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>1</v>
@@ -9265,33 +9516,33 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>7</v>
@@ -9302,13 +9553,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>9</v>
@@ -9319,13 +9570,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>6</v>
@@ -9344,13 +9595,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>5</v>
@@ -9358,13 +9609,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>5</v>
@@ -9372,13 +9623,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>5</v>
@@ -9386,13 +9637,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>5</v>
@@ -9400,13 +9651,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>4</v>
@@ -9414,13 +9665,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>3</v>
@@ -9428,13 +9679,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>7</v>
@@ -9445,13 +9696,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>6</v>
@@ -9462,13 +9713,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>5</v>

--- a/inasistencias-6A-electronicaYsistDeComTP/Alumnos-6A-EletronicaYsistDeComTP.xlsx
+++ b/inasistencias-6A-electronicaYsistDeComTP/Alumnos-6A-EletronicaYsistDeComTP.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="137">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -142,6 +142,9 @@
     <t xml:space="preserve">mateoibruno5@gmail.com</t>
   </si>
   <si>
+    <t xml:space="preserve">p</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mirko</t>
   </si>
   <si>
@@ -283,6 +286,9 @@
     <t xml:space="preserve">media falta</t>
   </si>
   <si>
+    <t xml:space="preserve">^</t>
+  </si>
+  <si>
     <t xml:space="preserve">resta</t>
   </si>
   <si>
@@ -361,13 +367,22 @@
     <t xml:space="preserve">informe</t>
   </si>
   <si>
-    <t xml:space="preserve">circuito</t>
+    <t xml:space="preserve">circuito tp4</t>
   </si>
   <si>
     <t xml:space="preserve">probado</t>
   </si>
   <si>
     <t xml:space="preserve">nota tp4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">circuito tp 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probado tp5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nota tp5</t>
   </si>
   <si>
     <t xml:space="preserve">mal</t>
@@ -506,7 +521,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -551,14 +566,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -572,7 +579,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="6">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -613,29 +620,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFCC0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -857,7 +841,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:FT1048576"/>
+  <dimension ref="A1:WYN27"/>
   <sheetFormatPr defaultColWidth="8.75390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
@@ -874,7 +858,8 @@
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="13" min="13" style="1" width="8.75"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="14" style="1" width="10.43"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="25" min="15" style="1" width="8.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16211" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="34" min="27" style="1" width="8.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16207" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -996,75 +981,63 @@
         <v>46217</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>46224</v>
+        <v>46259</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>46231</v>
+        <v>46266</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>46238</v>
+        <v>46273</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>46245</v>
-      </c>
-      <c r="AP2" s="3" t="n">
-        <v>46252</v>
+        <v>46280</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AQ2" s="3" t="n">
-        <v>46259</v>
+        <v>46287</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>46266</v>
+        <v>46294</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>46273</v>
+        <v>46301</v>
       </c>
       <c r="AT2" s="3" t="n">
-        <v>46280</v>
+        <v>46308</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46287</v>
+        <v>46315</v>
       </c>
       <c r="AV2" s="3" t="n">
-        <v>46294</v>
+        <v>46322</v>
       </c>
       <c r="AW2" s="3" t="n">
-        <v>46301</v>
+        <v>46329</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>46308</v>
+        <v>46336</v>
       </c>
       <c r="AY2" s="3" t="n">
-        <v>46315</v>
+        <v>46343</v>
       </c>
       <c r="AZ2" s="3" t="n">
-        <v>46322</v>
+        <v>46350</v>
       </c>
       <c r="BA2" s="3" t="n">
-        <v>46329</v>
+        <v>46357</v>
       </c>
       <c r="BB2" s="3" t="n">
-        <v>46336</v>
+        <v>46364</v>
       </c>
       <c r="BC2" s="3" t="n">
-        <v>46343</v>
+        <v>46371</v>
       </c>
       <c r="BD2" s="3" t="n">
-        <v>46350</v>
+        <v>46378</v>
       </c>
       <c r="BE2" s="3" t="n">
-        <v>46357</v>
-      </c>
-      <c r="BF2" s="3" t="n">
-        <v>46364</v>
-      </c>
-      <c r="BG2" s="3" t="n">
-        <v>46371</v>
-      </c>
-      <c r="BH2" s="3" t="n">
-        <v>46378</v>
-      </c>
-      <c r="BI2" s="3" t="n">
         <v>46385</v>
       </c>
     </row>
@@ -1157,7 +1130,28 @@
       <c r="AJ3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AK3" s="6" t="s">
+      <c r="AK3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS3" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1247,7 +1241,28 @@
       <c r="AJ4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AK4" s="6" t="s">
+      <c r="AK4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS4" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1337,8 +1352,32 @@
       <c r="AJ5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AK5" s="6" t="s">
-        <v>16</v>
+      <c r="AK5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP5" s="5" t="n">
+        <v>0.715277777777778</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS5" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1424,7 +1463,28 @@
       <c r="AJ6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AK6" s="6" t="s">
+      <c r="AK6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS6" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1517,7 +1577,28 @@
       <c r="AJ7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AK7" s="6" t="s">
+      <c r="AK7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS7" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1616,17 +1697,31 @@
       <c r="AJ8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AK8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL8" s="1"/>
-      <c r="AM8" s="1"/>
-      <c r="AN8" s="1"/>
-      <c r="AO8" s="1"/>
+      <c r="AK8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO8" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="AP8" s="1"/>
-      <c r="AQ8" s="1"/>
-      <c r="AR8" s="1"/>
-      <c r="AS8" s="1"/>
+      <c r="AQ8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS8" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="AT8" s="1"/>
       <c r="AU8" s="1"/>
       <c r="AV8" s="1"/>
@@ -1754,10 +1849,12 @@
       <c r="FN8" s="1"/>
       <c r="FO8" s="1"/>
       <c r="FP8" s="1"/>
-      <c r="FQ8" s="1"/>
-      <c r="FR8" s="1"/>
-      <c r="FS8" s="1"/>
-      <c r="FT8" s="1"/>
+      <c r="WYI8" s="1"/>
+      <c r="WYJ8" s="1"/>
+      <c r="WYK8" s="1"/>
+      <c r="WYL8" s="1"/>
+      <c r="WYM8" s="1"/>
+      <c r="WYN8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -1842,7 +1939,28 @@
       <c r="AJ9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AK9" s="6" t="s">
+      <c r="AK9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS9" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1851,13 +1969,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>14</v>
@@ -1929,7 +2047,28 @@
       <c r="AJ10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AK10" s="6" t="s">
+      <c r="AK10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS10" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1938,13 +2077,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>14</v>
@@ -2016,8 +2155,32 @@
       <c r="AJ11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AK11" s="6" t="s">
-        <v>16</v>
+      <c r="AK11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP11" s="5" t="n">
+        <v>0.715277777777778</v>
+      </c>
+      <c r="AQ11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS11" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="12" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2025,13 +2188,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>14</v>
@@ -2040,26 +2203,26 @@
         <v>16</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>16</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>16</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O12" s="7" t="s">
         <v>16</v>
@@ -2121,17 +2284,31 @@
       <c r="AJ12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AK12" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL12" s="1"/>
-      <c r="AM12" s="1"/>
-      <c r="AN12" s="1"/>
-      <c r="AO12" s="1"/>
+      <c r="AK12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO12" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="AP12" s="1"/>
-      <c r="AQ12" s="1"/>
-      <c r="AR12" s="1"/>
-      <c r="AS12" s="1"/>
+      <c r="AQ12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS12" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="AT12" s="1"/>
       <c r="AU12" s="1"/>
       <c r="AV12" s="1"/>
@@ -2144,10 +2321,10 @@
       <c r="BC12" s="1"/>
       <c r="BD12" s="1"/>
       <c r="BE12" s="1"/>
-      <c r="BF12" s="1"/>
-      <c r="BG12" s="1"/>
-      <c r="BH12" s="1"/>
-      <c r="BI12" s="1"/>
+      <c r="BF12" s="7"/>
+      <c r="BG12" s="7"/>
+      <c r="BH12" s="7"/>
+      <c r="BI12" s="7"/>
       <c r="BJ12" s="7"/>
       <c r="BK12" s="7"/>
       <c r="BL12" s="7"/>
@@ -2259,23 +2436,25 @@
       <c r="FN12" s="7"/>
       <c r="FO12" s="7"/>
       <c r="FP12" s="7"/>
-      <c r="FQ12" s="7"/>
-      <c r="FR12" s="7"/>
-      <c r="FS12" s="7"/>
-      <c r="FT12" s="7"/>
+      <c r="WYI12" s="1"/>
+      <c r="WYJ12" s="1"/>
+      <c r="WYK12" s="1"/>
+      <c r="WYL12" s="1"/>
+      <c r="WYM12" s="1"/>
+      <c r="WYN12" s="1"/>
     </row>
     <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>14</v>
@@ -2346,7 +2525,28 @@
       <c r="AJ13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AK13" s="6" t="s">
+      <c r="AK13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AS13" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2355,13 +2555,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>14</v>
@@ -2432,7 +2632,28 @@
       <c r="AJ14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AK14" s="6" t="s">
+      <c r="AK14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS14" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2441,13 +2662,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>14</v>
@@ -2456,26 +2677,26 @@
         <v>16</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H15" s="7"/>
       <c r="I15" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>16</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>16</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O15" s="7" t="s">
         <v>16</v>
@@ -2537,17 +2758,31 @@
       <c r="AJ15" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AK15" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL15" s="7"/>
-      <c r="AM15" s="7"/>
-      <c r="AN15" s="7"/>
-      <c r="AO15" s="7"/>
+      <c r="AK15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO15" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="AP15" s="7"/>
-      <c r="AQ15" s="7"/>
-      <c r="AR15" s="7"/>
-      <c r="AS15" s="7"/>
+      <c r="AQ15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS15" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="AT15" s="7"/>
       <c r="AU15" s="7"/>
       <c r="AV15" s="7"/>
@@ -2675,23 +2910,25 @@
       <c r="FN15" s="7"/>
       <c r="FO15" s="7"/>
       <c r="FP15" s="7"/>
-      <c r="FQ15" s="7"/>
-      <c r="FR15" s="7"/>
-      <c r="FS15" s="7"/>
-      <c r="FT15" s="7"/>
+      <c r="WYI15" s="1"/>
+      <c r="WYJ15" s="1"/>
+      <c r="WYK15" s="1"/>
+      <c r="WYL15" s="1"/>
+      <c r="WYM15" s="1"/>
+      <c r="WYN15" s="1"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>14</v>
@@ -2762,7 +2999,28 @@
       <c r="AJ16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AK16" s="6" t="s">
+      <c r="AK16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS16" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2771,13 +3029,13 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>14</v>
@@ -2848,7 +3106,28 @@
       <c r="AJ17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AK17" s="6" t="s">
+      <c r="AK17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS17" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2857,13 +3136,13 @@
         <v>16</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>14</v>
@@ -2872,14 +3151,14 @@
         <v>16</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>16</v>
@@ -2889,7 +3168,7 @@
         <v>16</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O18" s="7" t="s">
         <v>16</v>
@@ -2951,17 +3230,31 @@
       <c r="AJ18" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AK18" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL18" s="7"/>
-      <c r="AM18" s="7"/>
-      <c r="AN18" s="7"/>
-      <c r="AO18" s="7"/>
+      <c r="AK18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO18" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="AP18" s="7"/>
-      <c r="AQ18" s="7"/>
-      <c r="AR18" s="7"/>
-      <c r="AS18" s="7"/>
+      <c r="AQ18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS18" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="AT18" s="7"/>
       <c r="AU18" s="7"/>
       <c r="AV18" s="7"/>
@@ -3089,23 +3382,25 @@
       <c r="FN18" s="7"/>
       <c r="FO18" s="7"/>
       <c r="FP18" s="7"/>
-      <c r="FQ18" s="7"/>
-      <c r="FR18" s="7"/>
-      <c r="FS18" s="7"/>
-      <c r="FT18" s="7"/>
+      <c r="WYI18" s="1"/>
+      <c r="WYJ18" s="1"/>
+      <c r="WYK18" s="1"/>
+      <c r="WYL18" s="1"/>
+      <c r="WYM18" s="1"/>
+      <c r="WYN18" s="1"/>
     </row>
     <row r="19" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>14</v>
@@ -3127,7 +3422,7 @@
         <v>16</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O19" s="7" t="s">
         <v>16</v>
@@ -3189,17 +3484,31 @@
       <c r="AJ19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AK19" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL19" s="7"/>
-      <c r="AM19" s="7"/>
-      <c r="AN19" s="7"/>
-      <c r="AO19" s="7"/>
+      <c r="AK19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO19" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="AP19" s="7"/>
-      <c r="AQ19" s="7"/>
-      <c r="AR19" s="7"/>
-      <c r="AS19" s="7"/>
+      <c r="AQ19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS19" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="AT19" s="7"/>
       <c r="AU19" s="7"/>
       <c r="AV19" s="7"/>
@@ -3327,23 +3636,25 @@
       <c r="FN19" s="7"/>
       <c r="FO19" s="7"/>
       <c r="FP19" s="7"/>
-      <c r="FQ19" s="7"/>
-      <c r="FR19" s="7"/>
-      <c r="FS19" s="7"/>
-      <c r="FT19" s="7"/>
+      <c r="WYI19" s="1"/>
+      <c r="WYJ19" s="1"/>
+      <c r="WYK19" s="1"/>
+      <c r="WYL19" s="1"/>
+      <c r="WYM19" s="1"/>
+      <c r="WYN19" s="1"/>
     </row>
     <row r="20" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>14</v>
@@ -3361,7 +3672,7 @@
         <v>16</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O20" s="7" t="s">
         <v>16</v>
@@ -3417,22 +3728,49 @@
       <c r="AJ20" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AK20" s="6" t="s">
-        <v>16</v>
-      </c>
+      <c r="AK20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS20" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="WYI20" s="1"/>
+      <c r="WYJ20" s="1"/>
+      <c r="WYK20" s="1"/>
+      <c r="WYL20" s="1"/>
+      <c r="WYM20" s="1"/>
+      <c r="WYN20" s="1"/>
     </row>
     <row r="21" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>14</v>
@@ -3512,7 +3850,28 @@
       <c r="AJ21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AK21" s="6" t="s">
+      <c r="AK21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS21" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3521,13 +3880,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>14</v>
@@ -3598,7 +3957,28 @@
       <c r="AJ22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AK22" s="6" t="s">
+      <c r="AK22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS22" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3607,13 +3987,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>14</v>
@@ -3622,7 +4002,7 @@
         <v>16</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7" t="s">
@@ -3633,13 +4013,13 @@
         <v>16</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M23" s="7" t="s">
         <v>16</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O23" s="7" t="s">
         <v>16</v>
@@ -3701,17 +4081,31 @@
       <c r="AJ23" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AK23" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL23" s="7"/>
-      <c r="AM23" s="7"/>
-      <c r="AN23" s="7"/>
-      <c r="AO23" s="7"/>
+      <c r="AK23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO23" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="AP23" s="7"/>
-      <c r="AQ23" s="7"/>
-      <c r="AR23" s="7"/>
-      <c r="AS23" s="7"/>
+      <c r="AQ23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS23" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="AT23" s="7"/>
       <c r="AU23" s="7"/>
       <c r="AV23" s="7"/>
@@ -3839,10 +4233,12 @@
       <c r="FN23" s="7"/>
       <c r="FO23" s="7"/>
       <c r="FP23" s="7"/>
-      <c r="FQ23" s="7"/>
-      <c r="FR23" s="7"/>
-      <c r="FS23" s="7"/>
-      <c r="FT23" s="7"/>
+      <c r="WYI23" s="1"/>
+      <c r="WYJ23" s="1"/>
+      <c r="WYK23" s="1"/>
+      <c r="WYL23" s="1"/>
+      <c r="WYM23" s="1"/>
+      <c r="WYN23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
@@ -3892,9 +4288,6 @@
         <v>15</v>
       </c>
       <c r="Z24" s="1"/>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="1"/>
-      <c r="AC24" s="1"/>
       <c r="AD24" s="2" t="n">
         <f aca="false">COUNTIF(AD3:AD23,"P")</f>
         <v>15</v>
@@ -3920,10 +4313,39 @@
         <f aca="false">COUNTIF(AK3:AK23,"P")</f>
         <v>13</v>
       </c>
+      <c r="AL24" s="2" t="n">
+        <f aca="false">COUNTIF(AL3:AL23,"P")</f>
+        <v>12</v>
+      </c>
+      <c r="AM24" s="2" t="n">
+        <f aca="false">COUNTIF(AM3:AM23,"P")</f>
+        <v>16</v>
+      </c>
+      <c r="AN24" s="2" t="n">
+        <f aca="false">COUNTIF(AN3:AN23,"P")</f>
+        <v>15</v>
+      </c>
+      <c r="AO24" s="2" t="n">
+        <f aca="false">COUNTIF(AO3:AO23,"P")</f>
+        <v>12</v>
+      </c>
+      <c r="AP24" s="2"/>
+      <c r="AQ24" s="2" t="n">
+        <f aca="false">COUNTIF(AQ3:AQ23,"P")</f>
+        <v>15</v>
+      </c>
+      <c r="AR24" s="2" t="n">
+        <f aca="false">COUNTIF(AR3:AR23,"P")</f>
+        <v>12</v>
+      </c>
+      <c r="AS24" s="2" t="n">
+        <f aca="false">COUNTIF(AS3:AS23,"P")</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E25" s="1" t="n">
         <f aca="false">COUNTIF(E3:E23,"M")</f>
@@ -3966,9 +4388,6 @@
         <v>0</v>
       </c>
       <c r="Z25" s="1"/>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="1"/>
-      <c r="AC25" s="1"/>
       <c r="AF25" s="2" t="n">
         <f aca="false">COUNTIF(AF3:AF23,"M")</f>
         <v>0</v>
@@ -3984,6 +4403,38 @@
       <c r="AJ25" s="2" t="n">
         <f aca="false">COUNTIF(AJ3:AJ23,"M")</f>
         <v>0</v>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <f aca="false">COUNTIF(AK3:AK23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL25" s="2" t="n">
+        <f aca="false">COUNTIF(AL3:AL23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AM25" s="2" t="n">
+        <f aca="false">COUNTIF(AM3:AM23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AN25" s="2" t="n">
+        <f aca="false">COUNTIF(AN3:AN23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AO25" s="2" t="n">
+        <f aca="false">COUNTIF(AO3:AO23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AP25" s="2"/>
+      <c r="AQ25" s="2" t="n">
+        <f aca="false">COUNTIF(AQ3:AQ23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AR25" s="2" t="n">
+        <f aca="false">COUNTIF(AR3:AR23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AS25" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4031,9 +4482,6 @@
         <v>1</v>
       </c>
       <c r="Z26" s="1"/>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="1"/>
-      <c r="AC26" s="1"/>
       <c r="AF26" s="2" t="n">
         <f aca="false">COUNTIF(AF3:AF23,"T")</f>
         <v>2</v>
@@ -4050,6 +4498,39 @@
         <f aca="false">COUNTIF(AJ3:AJ23,"T")</f>
         <v>0</v>
       </c>
+      <c r="AK26" s="2" t="n">
+        <f aca="false">COUNTIF(AK3:AK23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AL26" s="2" t="n">
+        <f aca="false">COUNTIF(AL3:AL23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AM26" s="2" t="n">
+        <f aca="false">COUNTIF(AM3:AM23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AN26" s="2" t="n">
+        <f aca="false">COUNTIF(AN3:AN23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AO26" s="2" t="n">
+        <f aca="false">COUNTIF(AO3:AO23,"T")</f>
+        <v>2</v>
+      </c>
+      <c r="AP26" s="2"/>
+      <c r="AQ26" s="2" t="n">
+        <f aca="false">COUNTIF(AQ3:AQ23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AR26" s="2" t="n">
+        <f aca="false">COUNTIF(AR3:AR23,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AS26" s="2" t="n">
+        <f aca="false">COUNTIF(AS3:AS23,"T")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
@@ -4096,9 +4577,6 @@
         <v>16</v>
       </c>
       <c r="Z27" s="1"/>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="1"/>
-      <c r="AC27" s="1"/>
       <c r="AF27" s="2" t="n">
         <f aca="false">SUM(AF24:AF26)</f>
         <v>15</v>
@@ -4115,8 +4593,40 @@
         <f aca="false">SUM(AJ24:AJ26)</f>
         <v>15</v>
       </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="AK27" s="2" t="n">
+        <f aca="false">SUM(AK24:AK26)</f>
+        <v>13</v>
+      </c>
+      <c r="AL27" s="2" t="n">
+        <f aca="false">SUM(AL24:AL26)</f>
+        <v>12</v>
+      </c>
+      <c r="AM27" s="2" t="n">
+        <f aca="false">SUM(AM24:AM26)</f>
+        <v>16</v>
+      </c>
+      <c r="AN27" s="2" t="n">
+        <f aca="false">SUM(AN24:AN26)</f>
+        <v>15</v>
+      </c>
+      <c r="AO27" s="2" t="n">
+        <f aca="false">SUM(AO24:AO26)</f>
+        <v>14</v>
+      </c>
+      <c r="AP27" s="2"/>
+      <c r="AQ27" s="2" t="n">
+        <f aca="false">SUM(AQ24:AQ26)</f>
+        <v>15</v>
+      </c>
+      <c r="AR27" s="2" t="n">
+        <f aca="false">SUM(AR24:AR26)</f>
+        <v>12</v>
+      </c>
+      <c r="AS27" s="2" t="n">
+        <f aca="false">SUM(AS24:AS26)</f>
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="AB3:AB23">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -4171,6 +4681,8 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="1" width="27.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="16.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="44.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="10.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="997" min="997" style="1" width="9.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16355" style="1" width="10.58"/>
   </cols>
@@ -4178,13 +4690,13 @@
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="2"/>
       <c r="K1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AA1" s="3" t="n">
         <v>46189</v>
@@ -4201,102 +4713,109 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC2" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="AD2" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="AE2" s="6" t="s">
+      <c r="AC2" s="2" t="s">
         <v>113</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>9</v>
@@ -4349,7 +4868,7 @@
         <v>8</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AC3" s="1" t="n">
         <v>10</v>
@@ -4367,7 +4886,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C4" s="8" t="n">
         <v>1</v>
@@ -4444,13 +4963,13 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I5" s="1" t="n">
         <v>10</v>
@@ -4502,14 +5021,13 @@
       <c r="X5" s="2"/>
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
-      <c r="AA5" s="11" t="n">
+      <c r="AA5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="11" t="n">
+      <c r="AC5" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AD5" s="11" t="n">
+      <c r="AD5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AE5" s="1" t="n">
@@ -4522,7 +5040,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>1</v>
@@ -4578,14 +5096,13 @@
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
       <c r="Z6" s="7"/>
-      <c r="AA6" s="11" t="n">
+      <c r="AA6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AB6" s="11"/>
-      <c r="AC6" s="11" t="n">
+      <c r="AC6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AD6" s="11" t="n">
+      <c r="AD6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AE6" s="1" t="n">
@@ -4655,21 +5172,21 @@
       <c r="W7" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AA7" s="11" t="n">
+      <c r="AA7" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AB7" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="11" t="n">
+      <c r="AB7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC7" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AE7" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA7,AC7,AD7),0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4734,19 +5251,18 @@
       <c r="W8" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AA8" s="11" t="n">
+      <c r="AA8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD8" s="12" t="n">
+      <c r="AC8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AE8" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA8,AC8,AD8),0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="ALI8" s="1"/>
       <c r="ALJ8" s="1"/>
@@ -4851,19 +5367,18 @@
       <c r="W9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AA9" s="12" t="n">
+      <c r="AA9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD9" s="11" t="n">
+      <c r="AC9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AE9" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA9,AC9,AD9),0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" s="7" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4878,7 +5393,7 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -4934,21 +5449,21 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
-      <c r="AA10" s="11" t="n">
+      <c r="AA10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AB10" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="AC10" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="11" t="n">
-        <v>1</v>
+      <c r="AB10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD10" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="AE10" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA10,AC10,AD10),0)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5008,19 +5523,18 @@
       <c r="W11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AA11" s="11" t="n">
+      <c r="AA11" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD11" s="11" t="n">
-        <v>1</v>
+      <c r="AC11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="AE11" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA11,AC11,AD11),0)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5028,17 +5542,17 @@
         <v>15</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>4</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
@@ -5078,11 +5592,11 @@
       <c r="S12" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="T12" s="13" t="n">
+      <c r="T12" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(I12,L12,O12,R12,S12),0)</f>
         <v>7</v>
       </c>
-      <c r="U12" s="13" t="str">
+      <c r="U12" s="11" t="str">
         <f aca="false">IF(T12&gt;6,"TEA",IF(T12&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
@@ -5093,19 +5607,19 @@
       <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
-      <c r="AA12" s="11" t="n">
+      <c r="AA12" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AB12" s="12"/>
-      <c r="AC12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="12" t="n">
-        <v>1</v>
+      <c r="AB12" s="2"/>
+      <c r="AC12" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD12" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="AE12" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA12,AC12,AD12),0)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="ALI12" s="7"/>
       <c r="ALJ12" s="7"/>
@@ -5158,7 +5672,7 @@
         <v>20</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>4</v>
@@ -5212,19 +5726,18 @@
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
       <c r="Z13" s="7"/>
-      <c r="AA13" s="11" t="n">
+      <c r="AA13" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD13" s="11" t="n">
-        <v>1</v>
+      <c r="AC13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="AE13" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA13,AC13,AD13),0)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5289,21 +5802,27 @@
       <c r="W14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AA14" s="11" t="n">
+      <c r="AA14" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AB14" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="AC14" s="11" t="n">
+      <c r="AB14" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AC14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AD14" s="11" t="n">
-        <v>1</v>
+      <c r="AD14" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="AE14" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA14,AC14,AD14),0)</f>
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="AF14" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG14" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5311,13 +5830,13 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -5359,11 +5878,11 @@
       <c r="S15" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T15" s="13" t="n">
+      <c r="T15" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(I15,L15,O15,R15,S15),0)</f>
         <v>-2</v>
       </c>
-      <c r="U15" s="13" t="str">
+      <c r="U15" s="11" t="str">
         <f aca="false">IF(T15&gt;6,"TEA",IF(T15&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
@@ -5373,24 +5892,30 @@
       </c>
       <c r="X15" s="2"/>
       <c r="Y15" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AA15" s="11" t="n">
+        <v>129</v>
+      </c>
+      <c r="AA15" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AB15" s="12"/>
-      <c r="AC15" s="12" t="n">
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="AD15" s="12" t="n">
-        <v>1</v>
+      <c r="AD15" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="AE15" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA15,AC15,AD15),0)</f>
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="AF15" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG15" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="ALI15" s="7"/>
       <c r="ALJ15" s="7"/>
@@ -5443,7 +5968,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>5</v>
@@ -5501,19 +6026,24 @@
       <c r="W16" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AA16" s="11" t="n">
+      <c r="AA16" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AB16" s="11"/>
-      <c r="AC16" s="11" t="n">
+      <c r="AC16" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AD16" s="11" t="n">
-        <v>1</v>
+      <c r="AD16" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="AE16" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA16,AC16,AD16),0)</f>
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="AF16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG16" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5521,14 +6051,14 @@
         <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -5583,16 +6113,21 @@
       <c r="AA17" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AB17" s="11"/>
-      <c r="AC17" s="11" t="n">
+      <c r="AC17" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="AD17" s="11" t="n">
-        <v>1</v>
+      <c r="AD17" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="AE17" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA17,AC17,AD17),0)</f>
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="AF17" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG17" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5600,13 +6135,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>5</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
@@ -5648,11 +6183,11 @@
       <c r="S18" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T18" s="13" t="n">
+      <c r="T18" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(I18,L18,O18,R18,S18),0)</f>
         <v>-2</v>
       </c>
-      <c r="U18" s="13" t="str">
+      <c r="U18" s="11" t="str">
         <f aca="false">IF(T18&gt;6,"TEA",IF(T18&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
@@ -5666,16 +6201,22 @@
       <c r="AA18" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AB18" s="12"/>
-      <c r="AC18" s="12" t="n">
+      <c r="AB18" s="2"/>
+      <c r="AC18" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="AD18" s="12" t="n">
-        <v>1</v>
+      <c r="AD18" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="AE18" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(AA18,AC18,AD18),0)</f>
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="AF18" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG18" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="ALI18" s="7"/>
       <c r="ALJ18" s="7"/>
@@ -5728,7 +6269,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>100</v>
@@ -5774,11 +6315,11 @@
       <c r="S19" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T19" s="13" t="n">
+      <c r="T19" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(I19,L19,O19,R19,S19),0)</f>
         <v>-2</v>
       </c>
-      <c r="U19" s="13" t="str">
+      <c r="U19" s="11" t="str">
         <f aca="false">IF(T19&gt;6,"TEA",IF(T19&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
@@ -5840,7 +6381,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" s="8" t="n">
         <v>100</v>
@@ -5881,11 +6422,11 @@
       <c r="S20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T20" s="13" t="n">
+      <c r="T20" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(I20,L20,O20,R20,S20),0)</f>
         <v>-2</v>
       </c>
-      <c r="U20" s="13" t="str">
+      <c r="U20" s="11" t="str">
         <f aca="false">IF(T20&gt;6,"TEA",IF(T20&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
@@ -5899,13 +6440,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>100</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -5962,7 +6503,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>100</v>
@@ -7042,7 +7583,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>100</v>
@@ -7088,11 +7629,11 @@
       <c r="S23" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="T23" s="13" t="n">
+      <c r="T23" s="11" t="n">
         <f aca="false">ROUND(AVERAGE(I23,L23,O23,R23,S23),0)</f>
         <v>-2</v>
       </c>
-      <c r="U23" s="13" t="str">
+      <c r="U23" s="11" t="str">
         <f aca="false">IF(T23&gt;6,"TEA",IF(T23&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
@@ -8074,23 +8615,23 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="T2:U23">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>"TEA"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>"TEP"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"TED"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8138,7 +8679,7 @@
         <v>45961</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8272,7 +8813,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>4</v>
@@ -8293,7 +8834,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>3</v>
@@ -8308,7 +8849,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>3</v>
@@ -8323,7 +8864,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>3</v>
@@ -8344,7 +8885,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0</v>
@@ -8359,7 +8900,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>3</v>
@@ -8380,7 +8921,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>3</v>
@@ -8401,7 +8942,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>3</v>
@@ -8419,7 +8960,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>0</v>
@@ -8434,7 +8975,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>3</v>
@@ -8452,7 +8993,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>0</v>
@@ -8470,7 +9011,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20" s="1" t="n">
         <v>3</v>
@@ -8485,7 +9026,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>3</v>
@@ -8503,7 +9044,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>3</v>
@@ -8521,7 +9062,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1" t="n">
         <v>3</v>
@@ -8565,10 +9106,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8702,10 +9243,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>10</v>
@@ -8720,10 +9261,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>8</v>
@@ -8738,7 +9279,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>0</v>
@@ -8753,10 +9294,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>10</v>
@@ -8771,10 +9312,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>8</v>
@@ -8789,7 +9330,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>0</v>
@@ -8804,10 +9345,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>10</v>
@@ -8822,10 +9363,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>8</v>
@@ -8840,7 +9381,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>0</v>
@@ -8855,7 +9396,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>0</v>
@@ -8870,7 +9411,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>0</v>
@@ -8885,10 +9426,10 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>10</v>
@@ -8903,10 +9444,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>6</v>
@@ -8921,7 +9462,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>0</v>
@@ -8966,10 +9507,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9094,10 +9635,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>5</v>
@@ -9112,10 +9653,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>5</v>
@@ -9130,7 +9671,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>5</v>
@@ -9145,10 +9686,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>4</v>
@@ -9163,10 +9704,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>5</v>
@@ -9181,7 +9722,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>0</v>
@@ -9196,10 +9737,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>5</v>
@@ -9214,10 +9755,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>5</v>
@@ -9232,7 +9773,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>0</v>
@@ -9247,7 +9788,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>0</v>
@@ -9262,7 +9803,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>0</v>
@@ -9277,10 +9818,10 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>5</v>
@@ -9295,10 +9836,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>5</v>
@@ -9313,7 +9854,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>0</v>
@@ -9357,10 +9898,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9494,10 +10035,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>5</v>
@@ -9512,10 +10053,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>5</v>
@@ -9530,10 +10071,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>4</v>
@@ -9548,10 +10089,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>5</v>
@@ -9566,10 +10107,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>5</v>
@@ -9584,7 +10125,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>0</v>
@@ -9599,7 +10140,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>5</v>
@@ -9614,10 +10155,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>3</v>
@@ -9632,7 +10173,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>0</v>
@@ -9647,7 +10188,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>0</v>
@@ -9662,7 +10203,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>0</v>
@@ -9677,10 +10218,10 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>4</v>
@@ -9695,10 +10236,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>4</v>
@@ -9713,7 +10254,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>0</v>
@@ -9758,7 +10299,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9864,10 +10405,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>9</v>
@@ -9878,10 +10419,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>10</v>
@@ -9892,10 +10433,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>10</v>
@@ -9906,10 +10447,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>9</v>
@@ -9920,10 +10461,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>10</v>
@@ -9934,7 +10475,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>1</v>
@@ -9945,10 +10486,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>10</v>
@@ -9959,10 +10500,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>10</v>
@@ -9973,7 +10514,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>1</v>
@@ -9984,7 +10525,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>1</v>
@@ -9995,7 +10536,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>1</v>
@@ -10006,10 +10547,10 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>10</v>
@@ -10020,10 +10561,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>10</v>
@@ -10034,7 +10575,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>1</v>
